--- a/6_Quality Appraisal/Quality_Appraisal.xlsx
+++ b/6_Quality Appraisal/Quality_Appraisal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antoniotrovato/Documents/GitHub/RegressionTestingOptimizationSLR/6_Quality Appraisal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCBA6C62-F01F-6A40-949A-384EEDFE9D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9761DB-2E52-2048-8A77-5755A6539218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="620" windowWidth="28800" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <author>tc={ACAF5DB7-39A9-DA4F-81D5-ACC0A1571768}</author>
   </authors>
   <commentList>
-    <comment ref="AX125" authorId="0" shapeId="0" xr:uid="{ACAF5DB7-39A9-DA4F-81D5-ACC0A1571768}">
+    <comment ref="AX123" authorId="0" shapeId="0" xr:uid="{ACAF5DB7-39A9-DA4F-81D5-ACC0A1571768}">
       <text>
         <t>[Commento in thread]
 La versione di Excel in uso consente di leggere questo commento in thread, ma tutte le modifiche a esso apportate verranno rimosse se il file viene aperto in una versione più recente di Excel. Ulteriori informazioni: https://go.microsoft.com/fwlink/?linkid=870924
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="1324">
   <si>
     <t>ID</t>
   </si>
@@ -3058,15 +3058,6 @@
   </si>
   <si>
     <t>Test-case prioritization, proposed at the end of last century, aims to schedule the execution order of test cases so as to improve test effectiveness. In the past years, test-case prioritization has gained much attention, and has significant achievements in five aspects: prioritization algorithms, coverage criteria, measurement, practical concerns involved, and application scenarios. In this article, we will first review the achievements of test-case prioritization from these five aspects and then give our perspectives on its challenges.</t>
-  </si>
-  <si>
-    <t>R Mukherjee, KS Patnaik</t>
-  </si>
-  <si>
-    <t>Journal of King Saud University-Computer and Information Sciences, 2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> A survey on different approaches for software test case prioritization</t>
   </si>
   <si>
     <t>O Dahiya, K Solanki</t>
@@ -3114,12 +3105,6 @@
 The solution delivers optimal results in pseudo-polynomial time complexity, is effective for amounts of test cases up to the order of millions and compared with the classical dynamic programming methods leads to higher number of test cases to be involved in the selection process due to reduced memory consumption.</t>
   </si>
   <si>
-    <t>MJ Arafeen, H Do</t>
-  </si>
-  <si>
-    <t>Test case prioritization using requirements-based clustering</t>
-  </si>
-  <si>
     <t>Christopher Henard, Mike Papadakis, Mark Harman, Yue Jia, Yves Le Traon</t>
   </si>
   <si>
@@ -3169,19 +3154,6 @@
 Regression test case selection techniques attempt to increase the testing effectiveness based on the measurement capabilities, such as cost, coverage, and fault detection. This systematic literature review presents state-of-the-art research in effective regression test case selection techniques. We examined 47 empirical studies published between 2007 and 2015. The selected studies are categorized according to the selection procedure, empirical study design, and adequacy criteria with respect to their effectiveness measurement capability and methods used to measure the validity of these results.
 The results showed that mining and learning-based regression test case selection was reported in 39% of the studies, unit level testing was reported in 18% of the studies, and object-oriented environment (Java) was used in 26% of the studies. Structural faults, the most common target, was used in 55% of the studies. Overall, only 39% of the studies conducted followed experimental guidelines and are reproducible.
 There are 7 different cost measures, 13 different coverage types, and 5 fault-detection metrics reported in these studies. It is also observed that 70% of the studies being analyzed used cost as the effectiveness measure compared to 31% that used fault-detection capability and 16% that used coverage.</t>
-  </si>
-  <si>
-    <t>A Choudhary, AP Agrawal, A Kaur</t>
-  </si>
-  <si>
-    <t>Proceedings of the 11th International Workshop on Search-Based Software Testing, 2018</t>
-  </si>
-  <si>
-    <t>An effective approach for regression test case selection using pareto based multi-objective harmony search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Regression testing is a way of catching bugs in new builds and releases to avoid the product risks. Corrective, progressive, retest all and selective regression testing are strategies to perform regression testing. Retesting all existing test cases is one of the most reliable approaches but it is costly in terms of time and effort. This limitation opened a scope to optimize regression testing cost by selecting only a subset of test cases that can detect faults in optimal time and effort. This paper proposes Pareto based Multi-Objective Harmony Search approach for regression test case selection from an existing test suite to achieve some test adequacy criteria. Fault coverage, unique faults covered and algorithm execution time are utilised as performance measures to achieve optimization criteria. The performance evaluation of proposed approach is performed against Bat Search and Cuckoo Search optimization. The results of statistical tests indicate significant improvement over existing approaches.</t>
   </si>
   <si>
     <t>DK Yadav, S Dutta</t>
@@ -3324,30 +3296,6 @@
   </si>
   <si>
     <t>Luigi: toy examples</t>
-  </si>
-  <si>
-    <t>Jianlei Chia, Yu Quc, Qinghua Zhenga, Zijiang Yangb, Wuxia Jina, Di Cuia, Ting Liua</t>
-  </si>
-  <si>
-    <t>The Journal of Systems and Software</t>
-  </si>
-  <si>
-    <t>Test case prioritization (TCP), which aims at detecting faults as early as possible is broadly used in pro-
-gram regression testing. Most existing TCP techniques exploit coverage information with the hypothesis
-that higher coverage has more chance to catch bugs. Static structure information such as function and
-statement are frequently employed as coverage granularity. However, the former consumes less costs but
-presents lower capability to detect faults, the latter typically incurs more overhead.
-In this paper, dynamic function call sequences are argued that can guide TCP effectively. Same set of func-
-tions/statements can exhibit very different execution behaviors. Therefore, mapping program behaviors
-to unit-based (function/statement) coverage may not be enough to predict fault detection capability. We
-propose a new approach AGC (Additional Greedy method Call sequence). Our approach leverages dynamic
-relation-based coverage as measurement to extend the original additional greedy coverage algorithm in
-TCP techniques.
-We conduct our experiments on eight real-world java open source projects and systematically compare
-AGC against 22 state-of-the-art TCP techniques with different granularities. Results show that AGC out-
-performs existing techniques on large programs in terms of bug detection capability, and also achieves
-the highest mean APFD value. The performance demonstrates a growth trend as the size of the program
-increases.</t>
   </si>
   <si>
     <t>V Garousi, R Özkan, A Betin-Can</t>
@@ -4445,13 +4393,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>60</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4811,7 +4759,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -5974,7 +5922,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AX125" dT="2025-07-04T10:09:32.94" personId="{DD64DEE8-61CA-A04C-9DF2-0282913A9895}" id="{ACAF5DB7-39A9-DA4F-81D5-ACC0A1571768}">
+  <threadedComment ref="AX123" dT="2025-07-04T10:09:32.94" personId="{DD64DEE8-61CA-A04C-9DF2-0282913A9895}" id="{ACAF5DB7-39A9-DA4F-81D5-ACC0A1571768}">
     <text>da controllare</text>
   </threadedComment>
 </ThreadedComments>
@@ -5982,7 +5930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BM203"/>
+  <dimension ref="A1:BM199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.1640625" style="6" bestFit="1" customWidth="1"/>
@@ -6266,22 +6214,22 @@
       </c>
       <c r="BF2" s="7"/>
       <c r="BH2" s="5" t="s">
-        <v>1330</v>
+        <v>1318</v>
       </c>
       <c r="BI2" s="5" t="s">
-        <v>1331</v>
+        <v>1319</v>
       </c>
       <c r="BJ2" s="5" t="s">
-        <v>1332</v>
+        <v>1320</v>
       </c>
       <c r="BK2" s="5" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
       <c r="BL2" s="5" t="s">
-        <v>1334</v>
+        <v>1322</v>
       </c>
       <c r="BM2" s="5" t="s">
-        <v>1335</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="3" spans="1:65" ht="257" thickBot="1" x14ac:dyDescent="0.25">
@@ -6373,23 +6321,23 @@
         <v>78</v>
       </c>
       <c r="BI3" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"1,0",$AN$2:$AN$1000,"PS", $BE$2:$BE$1000,"&gt;=0,6")</f>
-        <v>60</v>
+        <f>COUNTIFS($AO$2:$AO$996,"1,0",$AN$2:$AN$996,"PS", $BE$2:$BE$996,"&gt;=0,6")</f>
+        <v>59</v>
       </c>
       <c r="BJ3" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,8",$AN$2:$AN$1000,"PS", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,8",$AN$2:$AN$996,"PS", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>24</v>
       </c>
       <c r="BK3" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,5",$AN$2:$AN$1000,"PS", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,5",$AN$2:$AN$996,"PS", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>17</v>
       </c>
       <c r="BL3" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,4",$AN$2:$AN$1000,"PS", $BE$2:$BE$1000,"&gt;=0,6")</f>
-        <v>9</v>
+        <f>COUNTIFS($AO$2:$AO$996,"0,4",$AN$2:$AN$996,"PS", $BE$2:$BE$996,"&gt;=0,6")</f>
+        <v>7</v>
       </c>
       <c r="BM3" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,2",$AN$2:$AN$1000,"PS", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,2",$AN$2:$AN$996,"PS", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>0</v>
       </c>
     </row>
@@ -6465,7 +6413,7 @@
         <v>0.63333333333333341</v>
       </c>
       <c r="BD4" s="13">
-        <f t="shared" ref="BD3:BD26" si="2">AVERAGE(BB4,BC4)</f>
+        <f t="shared" ref="BD4:BD26" si="2">AVERAGE(BB4,BC4)</f>
         <v>0.63333333333333341</v>
       </c>
       <c r="BE4" s="13">
@@ -6480,23 +6428,23 @@
         <v>151</v>
       </c>
       <c r="BI4" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"1,0",$AN$2:$AN$1000,"SLR", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"1,0",$AN$2:$AN$996,"SLR", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>4</v>
       </c>
       <c r="BJ4" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,8",$AN$2:$AN$1000,"SLR", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,8",$AN$2:$AN$996,"SLR", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>2</v>
       </c>
       <c r="BK4" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,5",$AN$2:$AN$1000,"SLR", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,5",$AN$2:$AN$996,"SLR", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>1</v>
       </c>
       <c r="BL4" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,4",$AN$2:$AN$1000,"SLR", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,4",$AN$2:$AN$996,"SLR", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>0</v>
       </c>
       <c r="BM4" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,2",$AN$2:$AN$1000,"SLR", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,2",$AN$2:$AN$996,"SLR", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>0</v>
       </c>
     </row>
@@ -6587,23 +6535,23 @@
         <v>67</v>
       </c>
       <c r="BI5" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"1,0",$AN$2:$AN$1000,"SR", $BE$2:$BE$1000,"&gt;=0,6")</f>
-        <v>5</v>
+        <f>COUNTIFS($AO$2:$AO$996,"1,0",$AN$2:$AN$996,"SR", $BE$2:$BE$996,"&gt;=0,6")</f>
+        <v>4</v>
       </c>
       <c r="BJ5" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,8",$AN$2:$AN$1000,"SR", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,8",$AN$2:$AN$996,"SR", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>2</v>
       </c>
       <c r="BK5" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,5",$AN$2:$AN$1000,"SR", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,5",$AN$2:$AN$996,"SR", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>1</v>
       </c>
       <c r="BL5" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,4",$AN$2:$AN$1000,"SR", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,4",$AN$2:$AN$996,"SR", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>0</v>
       </c>
       <c r="BM5" s="5">
-        <f>COUNTIFS($AO$2:$AO$1000,"0,2",$AN$2:$AN$1000,"SR", $BE$2:$BE$1000,"&gt;=0,6")</f>
+        <f>COUNTIFS($AO$2:$AO$996,"0,2",$AN$2:$AN$996,"SR", $BE$2:$BE$996,"&gt;=0,6")</f>
         <v>0</v>
       </c>
     </row>
@@ -13629,19 +13577,19 @@
       <c r="AV91" s="16"/>
       <c r="AW91" s="17"/>
       <c r="BB91" s="13">
-        <f t="shared" ref="BB91:BB154" si="8">AVERAGE(AP91,AR91,AT91,AV91,AX91,AZ91)</f>
+        <f t="shared" ref="BB91:BB150" si="8">AVERAGE(AP91,AR91,AT91,AV91,AX91,AZ91)</f>
         <v>0.3</v>
       </c>
       <c r="BC91" s="13">
-        <f t="shared" ref="BC91:BC154" si="9">AVERAGE(AQ91,AS91,AU91,AW91,AY91,BA91)</f>
+        <f t="shared" ref="BC91:BC150" si="9">AVERAGE(AQ91,AS91,AU91,AW91,AY91,BA91)</f>
         <v>0.3</v>
       </c>
       <c r="BD91" s="13">
-        <f t="shared" ref="BD91:BD154" si="10">AVERAGE(BB91,BC91)</f>
+        <f t="shared" ref="BD91:BD150" si="10">AVERAGE(BB91,BC91)</f>
         <v>0.3</v>
       </c>
       <c r="BE91" s="13">
-        <f t="shared" ref="BE91:BE154" si="11">AVERAGE(AO91,BD91)</f>
+        <f t="shared" ref="BE91:BE150" si="11">AVERAGE(AO91,BD91)</f>
         <v>0.65</v>
       </c>
     </row>
@@ -15411,7 +15359,7 @@
         <v>0.90833333333333321</v>
       </c>
     </row>
-    <row r="113" spans="3:57" ht="193" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:61" ht="193" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C113" s="7" t="s">
         <v>977</v>
       </c>
@@ -15470,7 +15418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="114" spans="3:61" ht="128" x14ac:dyDescent="0.2">
       <c r="C114" s="7" t="s">
         <v>981</v>
       </c>
@@ -15539,7 +15487,7 @@
         <v>0.54625000000000001</v>
       </c>
     </row>
-    <row r="115" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="115" spans="3:61" ht="128" x14ac:dyDescent="0.2">
       <c r="C115" s="7" t="s">
         <v>985</v>
       </c>
@@ -15598,7 +15546,7 @@
         <v>0.73333333333333339</v>
       </c>
     </row>
-    <row r="116" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="116" spans="3:61" ht="144" x14ac:dyDescent="0.2">
       <c r="C116" s="7" t="s">
         <v>989</v>
       </c>
@@ -15657,7 +15605,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="117" spans="3:57" ht="96" x14ac:dyDescent="0.2">
+    <row r="117" spans="3:61" ht="96" x14ac:dyDescent="0.2">
       <c r="C117" s="7" t="s">
         <v>993</v>
       </c>
@@ -15730,7 +15678,7 @@
         <v>0.52499999999999991</v>
       </c>
     </row>
-    <row r="118" spans="3:57" ht="65" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:61" ht="65" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C118" s="7" t="s">
         <v>997</v>
       </c>
@@ -15801,7 +15749,7 @@
         <v>0.745</v>
       </c>
     </row>
-    <row r="119" spans="3:57" ht="129" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:61" ht="113" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C119" s="7" t="s">
         <v>1001</v>
       </c>
@@ -15815,10 +15763,10 @@
         <v>2018</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>872</v>
+        <v>1004</v>
       </c>
       <c r="AN119" s="13" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="AO119" s="13">
         <v>1</v>
@@ -15826,152 +15774,140 @@
       <c r="AP119" s="15">
         <v>1</v>
       </c>
-      <c r="AQ119" s="16">
+      <c r="AQ119" s="17">
         <v>1</v>
       </c>
       <c r="AR119" s="15">
         <v>1</v>
       </c>
-      <c r="AS119" s="16">
+      <c r="AS119" s="17">
         <v>1</v>
       </c>
       <c r="AT119" s="15">
-        <v>1</v>
-      </c>
-      <c r="AU119" s="16">
-        <v>1</v>
+        <v>0.6</v>
+      </c>
+      <c r="AU119" s="17">
+        <v>0.6</v>
       </c>
       <c r="AV119" s="15">
-        <v>1</v>
-      </c>
-      <c r="AW119" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="AW119" s="17">
         <v>1</v>
       </c>
       <c r="AX119" s="15">
-        <v>1</v>
-      </c>
-      <c r="AY119" s="16">
-        <v>1</v>
+        <v>0.3</v>
+      </c>
+      <c r="AY119" s="17">
+        <v>0.3</v>
       </c>
       <c r="AZ119" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="BA119" s="16">
-        <v>0.6</v>
+        <v>0.3</v>
+      </c>
+      <c r="BA119" s="17">
+        <v>0.3</v>
       </c>
       <c r="BB119" s="13">
         <f t="shared" si="8"/>
-        <v>0.93333333333333324</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="BC119" s="13">
         <f t="shared" si="9"/>
-        <v>0.93333333333333324</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="BD119" s="13">
         <f t="shared" si="10"/>
-        <v>0.93333333333333324</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="BE119" s="13">
         <f t="shared" si="11"/>
-        <v>0.96666666666666656</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="120" spans="3:57" ht="112" x14ac:dyDescent="0.2">
+    <row r="120" spans="3:61" ht="144" x14ac:dyDescent="0.2">
       <c r="C120" s="7" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F120" s="13">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="J120" s="7" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="AN120" s="13" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AO120" s="13">
-        <v>1</v>
-      </c>
-      <c r="AP120" s="15">
-        <v>1</v>
-      </c>
-      <c r="AQ120" s="17">
-        <v>1</v>
-      </c>
-      <c r="AR120" s="15">
-        <v>1</v>
-      </c>
-      <c r="AS120" s="17">
-        <v>1</v>
-      </c>
-      <c r="AT120" s="15">
-        <v>0.6</v>
+        <v>0.5</v>
+      </c>
+      <c r="AP120" s="14">
+        <v>1</v>
+      </c>
+      <c r="AQ120" s="13">
+        <v>1</v>
+      </c>
+      <c r="AR120" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS120" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT120" s="16">
+        <v>1</v>
       </c>
       <c r="AU120" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="AV120" s="15">
-        <v>0.6</v>
+        <v>1</v>
+      </c>
+      <c r="AV120" s="16">
+        <v>1</v>
       </c>
       <c r="AW120" s="17">
         <v>1</v>
-      </c>
-      <c r="AX120" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="AY120" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="AZ120" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="BA120" s="17">
-        <v>0.3</v>
       </c>
       <c r="BB120" s="13">
         <f t="shared" si="8"/>
-        <v>0.6333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BC120" s="13">
         <f t="shared" si="9"/>
-        <v>0.70000000000000007</v>
+        <v>1</v>
       </c>
       <c r="BD120" s="13">
         <f t="shared" si="10"/>
-        <v>0.66666666666666674</v>
+        <v>1</v>
       </c>
       <c r="BE120" s="13">
         <f t="shared" si="11"/>
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
     </row>
-    <row r="121" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="121" spans="3:61" ht="305" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C121" s="7" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F121" s="13">
         <v>2019</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="AN121" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO121" s="13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP121" s="14">
         <v>1</v>
@@ -15985,50 +15921,46 @@
       <c r="AS121" s="13">
         <v>1</v>
       </c>
-      <c r="AT121" s="16">
-        <v>1</v>
-      </c>
-      <c r="AU121" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV121" s="16">
-        <v>1</v>
-      </c>
-      <c r="AW121" s="17">
-        <v>1</v>
-      </c>
+      <c r="AT121" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="AU121" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="AV121" s="14"/>
+      <c r="AW121" s="15"/>
       <c r="BB121" s="13">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BC121" s="13">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BD121" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BE121" s="13">
         <f t="shared" si="11"/>
-        <v>0.75</v>
+        <v>0.8833333333333333</v>
       </c>
     </row>
-    <row r="122" spans="3:57" ht="304" x14ac:dyDescent="0.2">
+    <row r="122" spans="3:61" ht="129" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C122" s="7" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F122" s="13">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="AN122" s="13" t="s">
         <v>78</v>
@@ -16043,110 +15975,126 @@
         <v>1</v>
       </c>
       <c r="AR122" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS122" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT122" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="AU122" s="15">
-        <v>0.3</v>
+        <v>1</v>
+      </c>
+      <c r="AU122" s="17">
+        <v>1</v>
       </c>
       <c r="AV122" s="14"/>
-      <c r="AW122" s="15"/>
+      <c r="AW122" s="17"/>
       <c r="BB122" s="13">
         <f t="shared" si="8"/>
-        <v>0.76666666666666661</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BC122" s="13">
         <f t="shared" si="9"/>
-        <v>0.76666666666666661</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BD122" s="13">
         <f t="shared" si="10"/>
-        <v>0.76666666666666661</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BE122" s="13">
         <f t="shared" si="11"/>
-        <v>0.8833333333333333</v>
+        <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="123" spans="3:57" ht="112" x14ac:dyDescent="0.2">
+    <row r="123" spans="3:61" ht="208" x14ac:dyDescent="0.2">
       <c r="C123" s="7" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>990</v>
+        <v>1018</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="F123" s="13">
         <v>2013</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>465</v>
+        <v>1020</v>
       </c>
       <c r="AN123" s="13" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="AO123" s="13">
-        <v>1</v>
-      </c>
-      <c r="AP123" s="14">
-        <v>1</v>
-      </c>
-      <c r="AQ123" s="13">
-        <v>1</v>
-      </c>
-      <c r="AR123" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS123" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT123" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="AP123" s="15">
+        <v>1</v>
+      </c>
+      <c r="AQ123" s="16">
+        <v>1</v>
+      </c>
+      <c r="AR123" s="15">
+        <v>1</v>
+      </c>
+      <c r="AS123" s="16">
+        <v>1</v>
+      </c>
+      <c r="AT123" s="15">
         <v>1</v>
       </c>
       <c r="AU123" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV123" s="14"/>
-      <c r="AW123" s="16"/>
+        <v>0.3</v>
+      </c>
+      <c r="AV123" s="15">
+        <v>1</v>
+      </c>
+      <c r="AW123" s="16">
+        <v>1</v>
+      </c>
+      <c r="AX123" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="AY123" s="16">
+        <v>0</v>
+      </c>
+      <c r="AZ123" s="15">
+        <v>0</v>
+      </c>
+      <c r="BA123" s="16">
+        <v>0</v>
+      </c>
       <c r="BB123" s="13">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BC123" s="13">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="BD123" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.64999999999999991</v>
       </c>
       <c r="BE123" s="13">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.72499999999999998</v>
       </c>
     </row>
-    <row r="124" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="124" spans="3:61" ht="144" x14ac:dyDescent="0.2">
       <c r="C124" s="7" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="F124" s="13">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="AN124" s="13" t="s">
         <v>78</v>
@@ -16161,132 +16109,132 @@
         <v>1</v>
       </c>
       <c r="AR124" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS124" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT124" s="14">
+        <v>1</v>
+      </c>
+      <c r="AT124" s="15">
         <v>1</v>
       </c>
       <c r="AU124" s="17">
         <v>1</v>
       </c>
-      <c r="AV124" s="14"/>
+      <c r="AV124" s="15"/>
       <c r="AW124" s="17"/>
       <c r="BB124" s="13">
         <f t="shared" si="8"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BC124" s="13">
         <f t="shared" si="9"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BD124" s="13">
         <f t="shared" si="10"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BE124" s="13">
         <f t="shared" si="11"/>
-        <v>0.83333333333333326</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="125" spans="3:57" ht="208" x14ac:dyDescent="0.2">
+    <row r="125" spans="3:61" ht="161" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C125" s="7" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="F125" s="13">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="AN125" s="13" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="AO125" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="AP125" s="15">
-        <v>1</v>
-      </c>
-      <c r="AQ125" s="16">
-        <v>1</v>
-      </c>
-      <c r="AR125" s="15">
-        <v>1</v>
-      </c>
-      <c r="AS125" s="16">
-        <v>1</v>
-      </c>
-      <c r="AT125" s="15">
-        <v>1</v>
-      </c>
-      <c r="AU125" s="16">
+        <v>1</v>
+      </c>
+      <c r="AP125" s="16">
+        <v>1</v>
+      </c>
+      <c r="AQ125" s="17">
+        <v>1</v>
+      </c>
+      <c r="AR125" s="16">
+        <v>1</v>
+      </c>
+      <c r="AS125" s="17">
+        <v>1</v>
+      </c>
+      <c r="AT125" s="16">
+        <v>1</v>
+      </c>
+      <c r="AU125" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV125" s="16">
+        <v>1</v>
+      </c>
+      <c r="AW125" s="17">
+        <v>1</v>
+      </c>
+      <c r="AX125" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="AY125" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="AZ125" s="16">
         <v>0.3</v>
       </c>
-      <c r="AV125" s="15">
-        <v>1</v>
-      </c>
-      <c r="AW125" s="16">
-        <v>1</v>
-      </c>
-      <c r="AX125" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="AY125" s="16">
-        <v>0</v>
-      </c>
-      <c r="AZ125" s="15">
-        <v>0</v>
-      </c>
-      <c r="BA125" s="16">
-        <v>0</v>
+      <c r="BA125" s="17">
+        <v>0.3</v>
       </c>
       <c r="BB125" s="13">
         <f t="shared" si="8"/>
-        <v>0.75</v>
+        <v>0.81666666666666654</v>
       </c>
       <c r="BC125" s="13">
         <f t="shared" si="9"/>
-        <v>0.54999999999999993</v>
+        <v>0.81666666666666654</v>
       </c>
       <c r="BD125" s="13">
         <f t="shared" si="10"/>
-        <v>0.64999999999999991</v>
+        <v>0.81666666666666654</v>
       </c>
       <c r="BE125" s="13">
         <f t="shared" si="11"/>
-        <v>0.72499999999999998</v>
+        <v>0.90833333333333321</v>
       </c>
     </row>
-    <row r="126" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="126" spans="3:61" ht="113" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C126" s="7" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="F126" s="13">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="AN126" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO126" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP126" s="14">
         <v>1</v>
@@ -16300,127 +16248,130 @@
       <c r="AS126" s="13">
         <v>1</v>
       </c>
-      <c r="AT126" s="15">
-        <v>1</v>
-      </c>
-      <c r="AU126" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV126" s="15"/>
-      <c r="AW126" s="17"/>
+      <c r="AT126" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="AU126" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="AV126" s="14"/>
+      <c r="AW126" s="16"/>
       <c r="BB126" s="13">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BC126" s="13">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BD126" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BE126" s="13">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="127" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="127" spans="3:61" ht="176" x14ac:dyDescent="0.2">
       <c r="C127" s="7" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="F127" s="13">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="AN127" s="13" t="s">
         <v>151</v>
       </c>
       <c r="AO127" s="13">
-        <v>1</v>
-      </c>
-      <c r="AP127" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="AP127" s="14">
         <v>1</v>
       </c>
       <c r="AQ127" s="17">
         <v>1</v>
       </c>
-      <c r="AR127" s="16">
+      <c r="AR127" s="14">
         <v>1</v>
       </c>
       <c r="AS127" s="17">
         <v>1</v>
       </c>
-      <c r="AT127" s="16">
-        <v>1</v>
+      <c r="AT127" s="14">
+        <v>0</v>
       </c>
       <c r="AU127" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV127" s="16">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AV127" s="14">
+        <v>0</v>
       </c>
       <c r="AW127" s="17">
-        <v>1</v>
-      </c>
-      <c r="AX127" s="16">
+        <v>0</v>
+      </c>
+      <c r="AX127" s="14">
+        <v>0</v>
+      </c>
+      <c r="AY127" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ127" s="14">
         <v>0.6</v>
       </c>
-      <c r="AY127" s="17">
+      <c r="BA127" s="17">
         <v>0.6</v>
-      </c>
-      <c r="AZ127" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="BA127" s="17">
-        <v>0.3</v>
       </c>
       <c r="BB127" s="13">
         <f t="shared" si="8"/>
-        <v>0.81666666666666654</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BC127" s="13">
         <f t="shared" si="9"/>
-        <v>0.81666666666666654</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BD127" s="13">
         <f t="shared" si="10"/>
-        <v>0.81666666666666654</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BE127" s="13">
         <f t="shared" si="11"/>
-        <v>0.90833333333333321</v>
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="BI127" s="5" t="s">
+        <v>1037</v>
       </c>
     </row>
-    <row r="128" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="128" spans="3:61" ht="144" x14ac:dyDescent="0.2">
       <c r="C128" s="7" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="F128" s="13">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="AN128" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO128" s="13">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AP128" s="14">
         <v>1</v>
@@ -16434,46 +16385,46 @@
       <c r="AS128" s="13">
         <v>1</v>
       </c>
-      <c r="AT128" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU128" s="15">
-        <v>1</v>
-      </c>
-      <c r="AV128" s="14"/>
-      <c r="AW128" s="15"/>
+      <c r="AT128" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU128" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="AV128" s="15"/>
+      <c r="AW128" s="16"/>
       <c r="BB128" s="13">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="BC128" s="13">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BD128" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="BE128" s="13">
         <f t="shared" si="11"/>
-        <v>0.7</v>
+        <v>0.94166666666666665</v>
       </c>
     </row>
-    <row r="129" spans="3:61" ht="112" x14ac:dyDescent="0.2">
+    <row r="129" spans="3:61" ht="160" x14ac:dyDescent="0.2">
       <c r="C129" s="7" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="F129" s="13">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="AN129" s="13" t="s">
         <v>78</v>
@@ -16493,124 +16444,105 @@
       <c r="AS129" s="13">
         <v>1</v>
       </c>
-      <c r="AT129" s="14">
+      <c r="AT129" s="15">
         <v>0.3</v>
       </c>
-      <c r="AU129" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="AV129" s="14"/>
-      <c r="AW129" s="16"/>
+      <c r="AU129" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV129" s="15"/>
+      <c r="AW129" s="17"/>
       <c r="BB129" s="13">
         <f t="shared" si="8"/>
         <v>0.76666666666666661</v>
       </c>
       <c r="BC129" s="13">
         <f t="shared" si="9"/>
-        <v>0.76666666666666661</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BD129" s="13">
         <f t="shared" si="10"/>
-        <v>0.76666666666666661</v>
+        <v>0.71666666666666656</v>
       </c>
       <c r="BE129" s="13">
         <f t="shared" si="11"/>
-        <v>0.6333333333333333</v>
+        <v>0.60833333333333328</v>
       </c>
     </row>
-    <row r="130" spans="3:61" ht="176" x14ac:dyDescent="0.2">
+    <row r="130" spans="3:61" ht="144" x14ac:dyDescent="0.2">
       <c r="C130" s="7" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="F130" s="13">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="AN130" s="13" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AO130" s="13">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AP130" s="14">
         <v>1</v>
       </c>
-      <c r="AQ130" s="17">
+      <c r="AQ130" s="13">
         <v>1</v>
       </c>
       <c r="AR130" s="14">
         <v>1</v>
       </c>
-      <c r="AS130" s="17">
-        <v>1</v>
-      </c>
-      <c r="AT130" s="14">
-        <v>0</v>
+      <c r="AS130" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT130" s="16">
+        <v>1</v>
       </c>
       <c r="AU130" s="17">
-        <v>0</v>
-      </c>
-      <c r="AV130" s="14">
-        <v>0</v>
-      </c>
-      <c r="AW130" s="17">
-        <v>0</v>
-      </c>
-      <c r="AX130" s="14">
-        <v>0</v>
-      </c>
-      <c r="AY130" s="17">
-        <v>0</v>
-      </c>
-      <c r="AZ130" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="BA130" s="17">
-        <v>0.6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AV130" s="16"/>
+      <c r="AW130" s="17"/>
       <c r="BB130" s="13">
         <f t="shared" si="8"/>
-        <v>0.43333333333333335</v>
+        <v>1</v>
       </c>
       <c r="BC130" s="13">
         <f t="shared" si="9"/>
-        <v>0.43333333333333335</v>
+        <v>1</v>
       </c>
       <c r="BD130" s="13">
         <f t="shared" si="10"/>
-        <v>0.43333333333333335</v>
+        <v>1</v>
       </c>
       <c r="BE130" s="13">
         <f t="shared" si="11"/>
-        <v>0.6166666666666667</v>
-      </c>
-      <c r="BI130" s="5" t="s">
-        <v>1046</v>
+        <v>0.7</v>
       </c>
     </row>
-    <row r="131" spans="3:61" ht="144" x14ac:dyDescent="0.2">
+    <row r="131" spans="3:61" ht="176" x14ac:dyDescent="0.2">
       <c r="C131" s="7" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="F131" s="13">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="AN131" s="13" t="s">
         <v>78</v>
@@ -16625,57 +16557,57 @@
         <v>1</v>
       </c>
       <c r="AR131" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS131" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT131" s="15">
-        <v>1</v>
-      </c>
-      <c r="AU131" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="AV131" s="15"/>
-      <c r="AW131" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="AT131" s="14">
+        <v>1</v>
+      </c>
+      <c r="AU131" s="15">
+        <v>1</v>
+      </c>
+      <c r="AV131" s="14"/>
+      <c r="AW131" s="15"/>
       <c r="BB131" s="13">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BC131" s="13">
         <f t="shared" si="9"/>
-        <v>0.76666666666666661</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BD131" s="13">
         <f t="shared" si="10"/>
-        <v>0.8833333333333333</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BE131" s="13">
         <f t="shared" si="11"/>
-        <v>0.94166666666666665</v>
+        <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="132" spans="3:61" ht="160" x14ac:dyDescent="0.2">
+    <row r="132" spans="3:61" ht="240" x14ac:dyDescent="0.2">
       <c r="C132" s="7" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="F132" s="13">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="AN132" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO132" s="13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP132" s="14">
         <v>1</v>
@@ -16689,52 +16621,52 @@
       <c r="AS132" s="13">
         <v>1</v>
       </c>
-      <c r="AT132" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="AU132" s="17">
-        <v>0</v>
-      </c>
-      <c r="AV132" s="15"/>
-      <c r="AW132" s="17"/>
+      <c r="AT132" s="14">
+        <v>1</v>
+      </c>
+      <c r="AU132" s="16">
+        <v>1</v>
+      </c>
+      <c r="AV132" s="14"/>
+      <c r="AW132" s="16"/>
       <c r="BB132" s="13">
         <f t="shared" si="8"/>
-        <v>0.76666666666666661</v>
+        <v>1</v>
       </c>
       <c r="BC132" s="13">
         <f t="shared" si="9"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BD132" s="13">
         <f t="shared" si="10"/>
-        <v>0.71666666666666656</v>
+        <v>1</v>
       </c>
       <c r="BE132" s="13">
         <f t="shared" si="11"/>
-        <v>0.60833333333333328</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="3:61" ht="144" x14ac:dyDescent="0.2">
       <c r="C133" s="7" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="F133" s="13">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="AN133" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO133" s="13">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AP133" s="14">
         <v>1</v>
@@ -16748,13 +16680,13 @@
       <c r="AS133" s="13">
         <v>1</v>
       </c>
-      <c r="AT133" s="16">
+      <c r="AT133" s="14">
         <v>1</v>
       </c>
       <c r="AU133" s="17">
         <v>1</v>
       </c>
-      <c r="AV133" s="16"/>
+      <c r="AV133" s="14"/>
       <c r="AW133" s="17"/>
       <c r="BB133" s="13">
         <f t="shared" si="8"/>
@@ -16770,24 +16702,24 @@
       </c>
       <c r="BE133" s="13">
         <f t="shared" si="11"/>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="134" spans="3:61" ht="176" x14ac:dyDescent="0.2">
+    <row r="134" spans="3:61" ht="96" x14ac:dyDescent="0.2">
       <c r="C134" s="7" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="F134" s="13">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="AN134" s="13" t="s">
         <v>78</v>
@@ -16802,51 +16734,51 @@
         <v>1</v>
       </c>
       <c r="AR134" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS134" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT134" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU134" s="15">
-        <v>1</v>
-      </c>
-      <c r="AV134" s="14"/>
-      <c r="AW134" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="AT134" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU134" s="16">
+        <v>1</v>
+      </c>
+      <c r="AV134" s="15"/>
+      <c r="AW134" s="16"/>
       <c r="BB134" s="13">
         <f t="shared" si="8"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BC134" s="13">
         <f t="shared" si="9"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BD134" s="13">
         <f t="shared" si="10"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BE134" s="13">
         <f t="shared" si="11"/>
-        <v>0.83333333333333326</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="135" spans="3:61" ht="240" x14ac:dyDescent="0.2">
+    <row r="135" spans="3:61" ht="176" x14ac:dyDescent="0.2">
       <c r="C135" s="7" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="F135" s="13">
         <v>2020</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="AN135" s="13" t="s">
         <v>78</v>
@@ -16866,14 +16798,14 @@
       <c r="AS135" s="13">
         <v>1</v>
       </c>
-      <c r="AT135" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU135" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV135" s="14"/>
-      <c r="AW135" s="16"/>
+      <c r="AT135" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU135" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV135" s="15"/>
+      <c r="AW135" s="17"/>
       <c r="BB135" s="13">
         <f t="shared" si="8"/>
         <v>1</v>
@@ -16891,27 +16823,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="3:61" ht="144" x14ac:dyDescent="0.2">
+    <row r="136" spans="3:61" ht="177" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C136" s="7" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="F136" s="13">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="AN136" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO136" s="13">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AP136" s="14">
         <v>1</v>
@@ -16925,46 +16857,49 @@
       <c r="AS136" s="13">
         <v>1</v>
       </c>
-      <c r="AT136" s="14">
-        <v>1</v>
+      <c r="AT136" s="16">
+        <v>0.3</v>
       </c>
       <c r="AU136" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV136" s="14"/>
+        <v>0</v>
+      </c>
+      <c r="AV136" s="16"/>
       <c r="AW136" s="17"/>
       <c r="BB136" s="13">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BC136" s="13">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BD136" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.71666666666666656</v>
       </c>
       <c r="BE136" s="13">
         <f t="shared" si="11"/>
-        <v>0.9</v>
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="BI136" s="5" t="s">
+        <v>1074</v>
       </c>
     </row>
-    <row r="137" spans="3:61" ht="96" x14ac:dyDescent="0.2">
+    <row r="137" spans="3:61" ht="321" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C137" s="7" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="F137" s="13">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="J137" s="7" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="AN137" s="13" t="s">
         <v>78</v>
@@ -16979,57 +16914,57 @@
         <v>1</v>
       </c>
       <c r="AR137" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS137" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT137" s="15">
+        <v>0</v>
+      </c>
+      <c r="AT137" s="14">
         <v>1</v>
       </c>
       <c r="AU137" s="16">
         <v>1</v>
       </c>
-      <c r="AV137" s="15"/>
+      <c r="AV137" s="14"/>
       <c r="AW137" s="16"/>
       <c r="BB137" s="13">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BC137" s="13">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BD137" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BE137" s="13">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="138" spans="3:61" ht="176" x14ac:dyDescent="0.2">
+    <row r="138" spans="3:61" ht="128" x14ac:dyDescent="0.2">
       <c r="C138" s="7" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="F138" s="13">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="J138" s="7" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="AN138" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO138" s="13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP138" s="14">
         <v>1</v>
@@ -17043,13 +16978,13 @@
       <c r="AS138" s="13">
         <v>1</v>
       </c>
-      <c r="AT138" s="15">
+      <c r="AT138" s="14">
         <v>1</v>
       </c>
       <c r="AU138" s="17">
         <v>1</v>
       </c>
-      <c r="AV138" s="15"/>
+      <c r="AV138" s="14"/>
       <c r="AW138" s="17"/>
       <c r="BB138" s="13">
         <f t="shared" si="8"/>
@@ -17065,30 +17000,30 @@
       </c>
       <c r="BE138" s="13">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="139" spans="3:61" ht="176" x14ac:dyDescent="0.2">
+    <row r="139" spans="3:61" ht="112" x14ac:dyDescent="0.2">
       <c r="C139" s="7" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="F139" s="13">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="J139" s="7" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="AN139" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO139" s="13">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AP139" s="14">
         <v>1</v>
@@ -17102,55 +17037,52 @@
       <c r="AS139" s="13">
         <v>1</v>
       </c>
-      <c r="AT139" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="AU139" s="17">
-        <v>0</v>
-      </c>
-      <c r="AV139" s="16"/>
-      <c r="AW139" s="17"/>
+      <c r="AT139" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU139" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="AV139" s="15"/>
+      <c r="AW139" s="16"/>
       <c r="BB139" s="13">
         <f t="shared" si="8"/>
-        <v>0.76666666666666661</v>
+        <v>1</v>
       </c>
       <c r="BC139" s="13">
         <f t="shared" si="9"/>
-        <v>0.66666666666666663</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BD139" s="13">
         <f t="shared" si="10"/>
-        <v>0.71666666666666656</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="BE139" s="13">
         <f t="shared" si="11"/>
-        <v>0.55833333333333335</v>
-      </c>
-      <c r="BI139" s="5" t="s">
-        <v>1083</v>
+        <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="140" spans="3:61" ht="256" x14ac:dyDescent="0.2">
+    <row r="140" spans="3:61" ht="160" x14ac:dyDescent="0.2">
       <c r="C140" s="7" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>911</v>
+        <v>1089</v>
       </c>
       <c r="F140" s="13">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="AN140" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO140" s="13">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AP140" s="14">
         <v>1</v>
@@ -17159,51 +17091,51 @@
         <v>1</v>
       </c>
       <c r="AR140" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS140" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT140" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU140" s="15">
-        <v>1</v>
-      </c>
-      <c r="AV140" s="14"/>
-      <c r="AW140" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="AT140" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="AU140" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="AV140" s="15"/>
+      <c r="AW140" s="17"/>
       <c r="BB140" s="13">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BC140" s="13">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BD140" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BE140" s="13">
         <f t="shared" si="11"/>
-        <v>0.7</v>
+        <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="141" spans="3:61" ht="320" x14ac:dyDescent="0.2">
+    <row r="141" spans="3:61" ht="144" x14ac:dyDescent="0.2">
       <c r="C141" s="7" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="F141" s="13">
         <v>2018</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="AN141" s="13" t="s">
         <v>78</v>
@@ -17218,110 +17150,110 @@
         <v>1</v>
       </c>
       <c r="AR141" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS141" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT141" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU141" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV141" s="14"/>
-      <c r="AW141" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="AT141" s="16">
+        <v>1</v>
+      </c>
+      <c r="AU141" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV141" s="16"/>
+      <c r="AW141" s="17"/>
       <c r="BB141" s="13">
         <f t="shared" si="8"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BC141" s="13">
         <f t="shared" si="9"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BD141" s="13">
         <f t="shared" si="10"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BE141" s="13">
         <f t="shared" si="11"/>
-        <v>0.83333333333333326</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="142" spans="3:61" ht="128" x14ac:dyDescent="0.2">
+    <row r="142" spans="3:61" ht="192" x14ac:dyDescent="0.2">
       <c r="C142" s="7" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="F142" s="13">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="AN142" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO142" s="13">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AP142" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ142" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR142" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS142" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT142" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU142" s="17">
-        <v>1</v>
+        <v>0.3</v>
+      </c>
+      <c r="AU142" s="15">
+        <v>0.3</v>
       </c>
       <c r="AV142" s="14"/>
-      <c r="AW142" s="17"/>
+      <c r="AW142" s="15"/>
       <c r="BB142" s="13">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="BC142" s="13">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="BD142" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="BE142" s="13">
         <f t="shared" si="11"/>
-        <v>0.9</v>
+        <v>0.25</v>
       </c>
     </row>
-    <row r="143" spans="3:61" ht="112" x14ac:dyDescent="0.2">
+    <row r="143" spans="3:61" ht="128" x14ac:dyDescent="0.2">
       <c r="C143" s="7" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="F143" s="13">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="AN143" s="13" t="s">
         <v>78</v>
@@ -17341,13 +17273,13 @@
       <c r="AS143" s="13">
         <v>1</v>
       </c>
-      <c r="AT143" s="15">
+      <c r="AT143" s="14">
         <v>1</v>
       </c>
       <c r="AU143" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AV143" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="AV143" s="14"/>
       <c r="AW143" s="16"/>
       <c r="BB143" s="13">
         <f t="shared" si="8"/>
@@ -17355,38 +17287,38 @@
       </c>
       <c r="BC143" s="13">
         <f t="shared" si="9"/>
-        <v>0.8666666666666667</v>
+        <v>1</v>
       </c>
       <c r="BD143" s="13">
         <f t="shared" si="10"/>
-        <v>0.93333333333333335</v>
+        <v>1</v>
       </c>
       <c r="BE143" s="13">
         <f t="shared" si="11"/>
-        <v>0.96666666666666667</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="144" spans="3:61" ht="160" x14ac:dyDescent="0.2">
+    <row r="144" spans="3:61" ht="144" x14ac:dyDescent="0.2">
       <c r="C144" s="7" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="F144" s="13">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="AN144" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO144" s="13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP144" s="14">
         <v>1</v>
@@ -17395,51 +17327,51 @@
         <v>1</v>
       </c>
       <c r="AR144" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS144" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT144" s="15">
-        <v>0.3</v>
+        <v>1</v>
+      </c>
+      <c r="AT144" s="14">
+        <v>0</v>
       </c>
       <c r="AU144" s="17">
         <v>0.3</v>
       </c>
-      <c r="AV144" s="15"/>
+      <c r="AV144" s="14"/>
       <c r="AW144" s="17"/>
       <c r="BB144" s="13">
         <f t="shared" si="8"/>
-        <v>0.43333333333333335</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BC144" s="13">
         <f t="shared" si="9"/>
-        <v>0.43333333333333335</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BD144" s="13">
         <f t="shared" si="10"/>
-        <v>0.43333333333333335</v>
+        <v>0.71666666666666656</v>
       </c>
       <c r="BE144" s="13">
         <f t="shared" si="11"/>
-        <v>0.71666666666666667</v>
+        <v>0.7583333333333333</v>
       </c>
     </row>
-    <row r="145" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="145" spans="3:57" ht="176" x14ac:dyDescent="0.2">
       <c r="C145" s="7" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="F145" s="13">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="AN145" s="13" t="s">
         <v>78</v>
@@ -17459,105 +17391,105 @@
       <c r="AS145" s="13">
         <v>1</v>
       </c>
-      <c r="AT145" s="16">
-        <v>1</v>
-      </c>
-      <c r="AU145" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV145" s="16"/>
-      <c r="AW145" s="17"/>
+      <c r="AT145" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU145" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="AV145" s="15"/>
+      <c r="AW145" s="16"/>
       <c r="BB145" s="13">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="BC145" s="13">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BD145" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="BE145" s="13">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="146" spans="3:57" ht="192" x14ac:dyDescent="0.2">
+    <row r="146" spans="3:57" ht="144" x14ac:dyDescent="0.2">
       <c r="C146" s="7" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F146" s="13">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="J146" s="7" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="AN146" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO146" s="13">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AP146" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ146" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR146" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS146" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT146" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="AU146" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="AV146" s="14"/>
-      <c r="AW146" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="AT146" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU146" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV146" s="15"/>
+      <c r="AW146" s="17"/>
       <c r="BB146" s="13">
         <f t="shared" si="8"/>
-        <v>9.9999999999999992E-2</v>
+        <v>1</v>
       </c>
       <c r="BC146" s="13">
         <f t="shared" si="9"/>
-        <v>9.9999999999999992E-2</v>
+        <v>1</v>
       </c>
       <c r="BD146" s="13">
         <f t="shared" si="10"/>
-        <v>9.9999999999999992E-2</v>
+        <v>1</v>
       </c>
       <c r="BE146" s="13">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="147" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="147" spans="3:57" ht="224" x14ac:dyDescent="0.2">
       <c r="C147" s="7" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="F147" s="13">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="J147" s="7" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="AN147" s="13" t="s">
         <v>78</v>
@@ -17577,14 +17509,14 @@
       <c r="AS147" s="13">
         <v>1</v>
       </c>
-      <c r="AT147" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU147" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV147" s="14"/>
-      <c r="AW147" s="16"/>
+      <c r="AT147" s="16">
+        <v>1</v>
+      </c>
+      <c r="AU147" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV147" s="16"/>
+      <c r="AW147" s="17"/>
       <c r="BB147" s="13">
         <f t="shared" si="8"/>
         <v>1</v>
@@ -17602,27 +17534,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="148" spans="3:57" ht="176" x14ac:dyDescent="0.2">
       <c r="C148" s="7" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="F148" s="13">
         <v>2014</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="AN148" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO148" s="13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP148" s="14">
         <v>1</v>
@@ -17637,45 +17569,45 @@
         <v>1</v>
       </c>
       <c r="AT148" s="14">
-        <v>0</v>
-      </c>
-      <c r="AU148" s="17">
-        <v>0.3</v>
+        <v>1</v>
+      </c>
+      <c r="AU148" s="15">
+        <v>1</v>
       </c>
       <c r="AV148" s="14"/>
-      <c r="AW148" s="17"/>
+      <c r="AW148" s="15"/>
       <c r="BB148" s="13">
         <f t="shared" si="8"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BC148" s="13">
         <f t="shared" si="9"/>
-        <v>0.76666666666666661</v>
+        <v>1</v>
       </c>
       <c r="BD148" s="13">
         <f t="shared" si="10"/>
-        <v>0.71666666666666656</v>
+        <v>1</v>
       </c>
       <c r="BE148" s="13">
         <f t="shared" si="11"/>
-        <v>0.7583333333333333</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="149" spans="3:57" ht="176" x14ac:dyDescent="0.2">
+    <row r="149" spans="3:57" ht="96" x14ac:dyDescent="0.2">
       <c r="C149" s="7" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="F149" s="13">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="J149" s="7" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="AN149" s="13" t="s">
         <v>78</v>
@@ -17690,57 +17622,57 @@
         <v>1</v>
       </c>
       <c r="AR149" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS149" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT149" s="15">
+        <v>0</v>
+      </c>
+      <c r="AT149" s="14">
         <v>1</v>
       </c>
       <c r="AU149" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AV149" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="AV149" s="14"/>
       <c r="AW149" s="16"/>
       <c r="BB149" s="13">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BC149" s="13">
         <f t="shared" si="9"/>
-        <v>0.8666666666666667</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BD149" s="13">
         <f t="shared" si="10"/>
-        <v>0.93333333333333335</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BE149" s="13">
         <f t="shared" si="11"/>
-        <v>0.96666666666666667</v>
+        <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="150" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="150" spans="3:57" ht="128" x14ac:dyDescent="0.2">
       <c r="C150" s="7" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="F150" s="13">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="J150" s="7" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="AN150" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO150" s="13">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AP150" s="14">
         <v>1</v>
@@ -17754,46 +17686,46 @@
       <c r="AS150" s="13">
         <v>1</v>
       </c>
-      <c r="AT150" s="15">
-        <v>1</v>
+      <c r="AT150" s="14">
+        <v>0</v>
       </c>
       <c r="AU150" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV150" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="AV150" s="14"/>
       <c r="AW150" s="17"/>
       <c r="BB150" s="13">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BC150" s="13">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BD150" s="13">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BE150" s="13">
         <f t="shared" si="11"/>
-        <v>0.9</v>
+        <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="151" spans="3:57" ht="224" x14ac:dyDescent="0.2">
+    <row r="151" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C151" s="7" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="F151" s="13">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="J151" s="7" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="AN151" s="13" t="s">
         <v>78</v>
@@ -17813,46 +17745,46 @@
       <c r="AS151" s="13">
         <v>1</v>
       </c>
-      <c r="AT151" s="16">
-        <v>1</v>
-      </c>
-      <c r="AU151" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV151" s="16"/>
-      <c r="AW151" s="17"/>
+      <c r="AT151" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU151" s="16">
+        <v>1</v>
+      </c>
+      <c r="AV151" s="15"/>
+      <c r="AW151" s="16"/>
       <c r="BB151" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="BB151:BB199" si="12">AVERAGE(AP151,AR151,AT151,AV151,AX151,AZ151)</f>
         <v>1</v>
       </c>
       <c r="BC151" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="BC151:BC199" si="13">AVERAGE(AQ151,AS151,AU151,AW151,AY151,BA151)</f>
         <v>1</v>
       </c>
       <c r="BD151" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="BD151:BD199" si="14">AVERAGE(BB151,BC151)</f>
         <v>1</v>
       </c>
       <c r="BE151" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="BE151:BE199" si="15">AVERAGE(AO151,BD151)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="3:57" ht="176" x14ac:dyDescent="0.2">
+    <row r="152" spans="3:57" ht="208" x14ac:dyDescent="0.2">
       <c r="C152" s="7" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="F152" s="13">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="J152" s="7" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="AN152" s="13" t="s">
         <v>78</v>
@@ -17861,10 +17793,10 @@
         <v>1</v>
       </c>
       <c r="AP152" s="14">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AQ152" s="13">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AR152" s="14">
         <v>1</v>
@@ -17872,105 +17804,105 @@
       <c r="AS152" s="13">
         <v>1</v>
       </c>
-      <c r="AT152" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU152" s="15">
-        <v>1</v>
-      </c>
-      <c r="AV152" s="14"/>
-      <c r="AW152" s="15"/>
+      <c r="AT152" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU152" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV152" s="15"/>
+      <c r="AW152" s="17"/>
       <c r="BB152" s="13">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <f t="shared" si="12"/>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BC152" s="13">
-        <f t="shared" si="9"/>
-        <v>1</v>
+        <f t="shared" si="13"/>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BD152" s="13">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="14"/>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BE152" s="13">
-        <f t="shared" si="11"/>
-        <v>1</v>
+        <f t="shared" si="15"/>
+        <v>0.93333333333333335</v>
       </c>
     </row>
     <row r="153" spans="3:57" ht="96" x14ac:dyDescent="0.2">
       <c r="C153" s="7" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="F153" s="13">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="AN153" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO153" s="13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP153" s="14">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AQ153" s="13">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AR153" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS153" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT153" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU153" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV153" s="14"/>
-      <c r="AW153" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="AT153" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="AU153" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="AV153" s="16"/>
+      <c r="AW153" s="17"/>
       <c r="BB153" s="13">
-        <f t="shared" si="8"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="12"/>
+        <v>0.6333333333333333</v>
       </c>
       <c r="BC153" s="13">
-        <f t="shared" si="9"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="13"/>
+        <v>0.6333333333333333</v>
       </c>
       <c r="BD153" s="13">
-        <f t="shared" si="10"/>
-        <v>0.66666666666666663</v>
+        <f t="shared" si="14"/>
+        <v>0.6333333333333333</v>
       </c>
       <c r="BE153" s="13">
-        <f t="shared" si="11"/>
-        <v>0.83333333333333326</v>
+        <f t="shared" si="15"/>
+        <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="154" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="154" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C154" s="7" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="F154" s="13">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="AN154" s="13" t="s">
         <v>78</v>
@@ -17979,10 +17911,10 @@
         <v>0.4</v>
       </c>
       <c r="AP154" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ154" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR154" s="14">
         <v>1</v>
@@ -17991,45 +17923,45 @@
         <v>1</v>
       </c>
       <c r="AT154" s="14">
-        <v>0</v>
-      </c>
-      <c r="AU154" s="17">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU154" s="15">
+        <v>1</v>
       </c>
       <c r="AV154" s="14"/>
-      <c r="AW154" s="17"/>
+      <c r="AW154" s="15"/>
       <c r="BB154" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="BC154" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="BD154" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="BE154" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="155" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="155" spans="3:57" ht="128" x14ac:dyDescent="0.2">
       <c r="C155" s="7" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="F155" s="13">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="J155" s="7" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="AN155" s="13" t="s">
         <v>78</v>
@@ -18049,46 +17981,46 @@
       <c r="AS155" s="13">
         <v>1</v>
       </c>
-      <c r="AT155" s="15">
+      <c r="AT155" s="14">
         <v>1</v>
       </c>
       <c r="AU155" s="16">
         <v>1</v>
       </c>
-      <c r="AV155" s="15"/>
+      <c r="AV155" s="14"/>
       <c r="AW155" s="16"/>
       <c r="BB155" s="13">
-        <f t="shared" ref="BB155:BB203" si="12">AVERAGE(AP155,AR155,AT155,AV155,AX155,AZ155)</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="BC155" s="13">
-        <f t="shared" ref="BC155:BC203" si="13">AVERAGE(AQ155,AS155,AU155,AW155,AY155,BA155)</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BD155" s="13">
-        <f t="shared" ref="BD155:BD203" si="14">AVERAGE(BB155,BC155)</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="BE155" s="13">
-        <f t="shared" ref="BE155:BE203" si="15">AVERAGE(AO155,BD155)</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="3:57" ht="208" x14ac:dyDescent="0.2">
+    <row r="156" spans="3:57" ht="144" x14ac:dyDescent="0.2">
       <c r="C156" s="7" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>1148</v>
+        <v>1051</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="F156" s="13">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="J156" s="7" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="AN156" s="13" t="s">
         <v>78</v>
@@ -18097,24 +18029,24 @@
         <v>1</v>
       </c>
       <c r="AP156" s="14">
+        <v>1</v>
+      </c>
+      <c r="AQ156" s="13">
+        <v>1</v>
+      </c>
+      <c r="AR156" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS156" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT156" s="14">
         <v>0.6</v>
       </c>
-      <c r="AQ156" s="13">
-        <v>0.6</v>
-      </c>
-      <c r="AR156" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS156" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT156" s="15">
-        <v>1</v>
-      </c>
       <c r="AU156" s="17">
         <v>1</v>
       </c>
-      <c r="AV156" s="15"/>
+      <c r="AV156" s="14"/>
       <c r="AW156" s="17"/>
       <c r="BB156" s="13">
         <f t="shared" si="12"/>
@@ -18122,103 +18054,103 @@
       </c>
       <c r="BC156" s="13">
         <f t="shared" si="13"/>
-        <v>0.8666666666666667</v>
+        <v>1</v>
       </c>
       <c r="BD156" s="13">
         <f t="shared" si="14"/>
-        <v>0.8666666666666667</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="BE156" s="13">
         <f t="shared" si="15"/>
-        <v>0.93333333333333335</v>
+        <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="157" spans="3:57" ht="96" x14ac:dyDescent="0.2">
+    <row r="157" spans="3:57" ht="176" x14ac:dyDescent="0.2">
       <c r="C157" s="7" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="F157" s="13">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="J157" s="7" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="AN157" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO157" s="13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP157" s="14">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AQ157" s="13">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AR157" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS157" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT157" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AU157" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="AV157" s="16"/>
-      <c r="AW157" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="AT157" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU157" s="16">
+        <v>1</v>
+      </c>
+      <c r="AV157" s="15"/>
+      <c r="AW157" s="16"/>
       <c r="BB157" s="13">
         <f t="shared" si="12"/>
-        <v>0.6333333333333333</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BC157" s="13">
         <f t="shared" si="13"/>
-        <v>0.6333333333333333</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BD157" s="13">
         <f t="shared" si="14"/>
-        <v>0.6333333333333333</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BE157" s="13">
         <f t="shared" si="15"/>
-        <v>0.71666666666666667</v>
+        <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="158" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="158" spans="3:57" ht="176" x14ac:dyDescent="0.2">
       <c r="C158" s="7" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>1156</v>
+        <v>1051</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="F158" s="13">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="J158" s="7" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="AN158" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO158" s="13">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AP158" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ158" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR158" s="14">
         <v>1</v>
@@ -18226,46 +18158,46 @@
       <c r="AS158" s="13">
         <v>1</v>
       </c>
-      <c r="AT158" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU158" s="15">
-        <v>1</v>
-      </c>
-      <c r="AV158" s="14"/>
-      <c r="AW158" s="15"/>
+      <c r="AT158" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU158" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV158" s="15"/>
+      <c r="AW158" s="17"/>
       <c r="BB158" s="13">
         <f t="shared" si="12"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BC158" s="13">
         <f t="shared" si="13"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BD158" s="13">
         <f t="shared" si="14"/>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="BE158" s="13">
         <f t="shared" si="15"/>
-        <v>0.53333333333333333</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="159" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="159" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C159" s="7" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>1160</v>
+        <v>1051</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F159" s="13">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="J159" s="7" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="AN159" s="13" t="s">
         <v>78</v>
@@ -18285,14 +18217,14 @@
       <c r="AS159" s="13">
         <v>1</v>
       </c>
-      <c r="AT159" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU159" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV159" s="14"/>
-      <c r="AW159" s="16"/>
+      <c r="AT159" s="16">
+        <v>1</v>
+      </c>
+      <c r="AU159" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV159" s="16"/>
+      <c r="AW159" s="17"/>
       <c r="BB159" s="13">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -18310,86 +18242,83 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="160" spans="3:57" ht="176" x14ac:dyDescent="0.2">
       <c r="C160" s="7" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>1060</v>
+        <v>1165</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="F160" s="13">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="J160" s="7" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="AN160" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO160" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP160" s="14">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AQ160" s="13">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AR160" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS160" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT160" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="AU160" s="17">
+        <v>1</v>
+      </c>
+      <c r="AU160" s="15">
         <v>1</v>
       </c>
       <c r="AV160" s="14"/>
-      <c r="AW160" s="17"/>
+      <c r="AW160" s="15"/>
       <c r="BB160" s="13">
         <f t="shared" si="12"/>
-        <v>0.8666666666666667</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BC160" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BD160" s="13">
         <f t="shared" si="14"/>
-        <v>0.93333333333333335</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BE160" s="13">
         <f t="shared" si="15"/>
-        <v>0.96666666666666667</v>
+        <v>0.51666666666666661</v>
       </c>
     </row>
-    <row r="161" spans="3:57" ht="176" x14ac:dyDescent="0.2">
+    <row r="161" spans="3:57" ht="112" x14ac:dyDescent="0.2">
       <c r="C161" s="7" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="F161" s="13">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="J161" s="7" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AN161" s="13" t="s">
-        <v>78</v>
+        <v>1171</v>
       </c>
       <c r="AO161" s="13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP161" s="14">
         <v>1</v>
@@ -18403,13 +18332,13 @@
       <c r="AS161" s="13">
         <v>0</v>
       </c>
-      <c r="AT161" s="15">
+      <c r="AT161" s="14">
         <v>1</v>
       </c>
       <c r="AU161" s="16">
         <v>1</v>
       </c>
-      <c r="AV161" s="15"/>
+      <c r="AV161" s="14"/>
       <c r="AW161" s="16"/>
       <c r="BB161" s="13">
         <f t="shared" si="12"/>
@@ -18425,30 +18354,30 @@
       </c>
       <c r="BE161" s="13">
         <f t="shared" si="15"/>
-        <v>0.83333333333333326</v>
+        <v>0.73333333333333339</v>
       </c>
     </row>
-    <row r="162" spans="3:57" ht="176" x14ac:dyDescent="0.2">
+    <row r="162" spans="3:57" ht="128" x14ac:dyDescent="0.2">
       <c r="C162" s="7" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>1060</v>
+        <v>1173</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="F162" s="13">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="J162" s="7" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="AN162" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO162" s="13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP162" s="14">
         <v>1</v>
@@ -18462,13 +18391,13 @@
       <c r="AS162" s="13">
         <v>1</v>
       </c>
-      <c r="AT162" s="15">
+      <c r="AT162" s="14">
         <v>1</v>
       </c>
       <c r="AU162" s="17">
         <v>1</v>
       </c>
-      <c r="AV162" s="15"/>
+      <c r="AV162" s="14"/>
       <c r="AW162" s="17"/>
       <c r="BB162" s="13">
         <f t="shared" si="12"/>
@@ -18484,24 +18413,24 @@
       </c>
       <c r="BE162" s="13">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
-    <row r="163" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="163" spans="3:57" ht="176" x14ac:dyDescent="0.2">
       <c r="C163" s="7" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>1060</v>
+        <v>1014</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="F163" s="13">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="J163" s="7" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="AN163" s="13" t="s">
         <v>78</v>
@@ -18516,51 +18445,51 @@
         <v>1</v>
       </c>
       <c r="AR163" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS163" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT163" s="16">
-        <v>1</v>
-      </c>
-      <c r="AU163" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV163" s="16"/>
-      <c r="AW163" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="AT163" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU163" s="16">
+        <v>1</v>
+      </c>
+      <c r="AV163" s="15"/>
+      <c r="AW163" s="16"/>
       <c r="BB163" s="13">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BC163" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BD163" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BE163" s="13">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0.83333333333333326</v>
       </c>
     </row>
-    <row r="164" spans="3:57" ht="176" x14ac:dyDescent="0.2">
+    <row r="164" spans="3:57" ht="192" x14ac:dyDescent="0.2">
       <c r="C164" s="7" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="F164" s="13">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="J164" s="7" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="AN164" s="13" t="s">
         <v>78</v>
@@ -18575,51 +18504,54 @@
         <v>0.6</v>
       </c>
       <c r="AR164" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS164" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT164" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU164" s="15">
-        <v>1</v>
-      </c>
-      <c r="AV164" s="14"/>
-      <c r="AW164" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="AT164" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="AU164" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="AV164" s="15"/>
+      <c r="AW164" s="17"/>
       <c r="BB164" s="13">
         <f t="shared" si="12"/>
-        <v>0.53333333333333333</v>
+        <v>0.63333333333333341</v>
       </c>
       <c r="BC164" s="13">
         <f t="shared" si="13"/>
-        <v>0.53333333333333333</v>
+        <v>0.63333333333333341</v>
       </c>
       <c r="BD164" s="13">
         <f t="shared" si="14"/>
-        <v>0.53333333333333333</v>
+        <v>0.63333333333333341</v>
       </c>
       <c r="BE164" s="13">
         <f t="shared" si="15"/>
-        <v>0.51666666666666661</v>
+        <v>0.56666666666666665</v>
       </c>
     </row>
     <row r="165" spans="3:57" ht="112" x14ac:dyDescent="0.2">
       <c r="C165" s="7" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="F165" s="13">
         <v>2015</v>
       </c>
       <c r="J165" s="7" t="s">
-        <v>1183</v>
+        <v>1186</v>
+      </c>
+      <c r="AN165" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="AO165" s="13">
         <v>0.8</v>
@@ -18636,58 +18568,58 @@
       <c r="AS165" s="13">
         <v>0</v>
       </c>
-      <c r="AT165" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU165" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV165" s="14"/>
-      <c r="AW165" s="16"/>
+      <c r="AT165" s="16">
+        <v>0</v>
+      </c>
+      <c r="AU165" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV165" s="16"/>
+      <c r="AW165" s="17"/>
       <c r="BB165" s="13">
         <f t="shared" si="12"/>
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BC165" s="13">
         <f t="shared" si="13"/>
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BD165" s="13">
         <f t="shared" si="14"/>
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BE165" s="13">
         <f t="shared" si="15"/>
-        <v>0.73333333333333339</v>
+        <v>0.56666666666666665</v>
       </c>
     </row>
-    <row r="166" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="166" spans="3:57" ht="144" x14ac:dyDescent="0.2">
       <c r="C166" s="7" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="F166" s="13">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="J166" s="7" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="AN166" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO166" s="13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP166" s="14">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AQ166" s="13">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AR166" s="14">
         <v>1</v>
@@ -18696,116 +18628,130 @@
         <v>1</v>
       </c>
       <c r="AT166" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU166" s="17">
-        <v>1</v>
+        <v>0.3</v>
+      </c>
+      <c r="AU166" s="15">
+        <v>0.3</v>
       </c>
       <c r="AV166" s="14"/>
-      <c r="AW166" s="17"/>
+      <c r="AW166" s="15"/>
       <c r="BB166" s="13">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BC166" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BD166" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BE166" s="13">
         <f t="shared" si="15"/>
-        <v>0.9</v>
+        <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="167" spans="3:57" ht="176" x14ac:dyDescent="0.2">
+    <row r="167" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C167" s="7" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>1019</v>
+        <v>1155</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="F167" s="13">
         <v>2016</v>
       </c>
       <c r="J167" s="7" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="AN167" s="13" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="AO167" s="13">
         <v>1</v>
       </c>
-      <c r="AP167" s="14">
-        <v>1</v>
-      </c>
-      <c r="AQ167" s="13">
-        <v>1</v>
+      <c r="AP167" s="14"/>
+      <c r="AQ167" s="16">
+        <v>0</v>
       </c>
       <c r="AR167" s="14">
-        <v>0</v>
-      </c>
-      <c r="AS167" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT167" s="15">
+        <v>1</v>
+      </c>
+      <c r="AS167" s="16">
+        <v>1</v>
+      </c>
+      <c r="AT167" s="14">
         <v>1</v>
       </c>
       <c r="AU167" s="16">
         <v>1</v>
       </c>
-      <c r="AV167" s="15"/>
-      <c r="AW167" s="16"/>
+      <c r="AV167" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="AW167" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="AX167" s="14">
+        <v>1</v>
+      </c>
+      <c r="AY167" s="16">
+        <v>1</v>
+      </c>
+      <c r="AZ167" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="BA167" s="16">
+        <v>0.3</v>
+      </c>
       <c r="BB167" s="13">
         <f t="shared" si="12"/>
-        <v>0.66666666666666663</v>
+        <v>0.72</v>
       </c>
       <c r="BC167" s="13">
         <f t="shared" si="13"/>
-        <v>0.66666666666666663</v>
+        <v>0.6</v>
       </c>
       <c r="BD167" s="13">
         <f t="shared" si="14"/>
-        <v>0.66666666666666663</v>
+        <v>0.65999999999999992</v>
       </c>
       <c r="BE167" s="13">
         <f t="shared" si="15"/>
-        <v>0.83333333333333326</v>
+        <v>0.83</v>
       </c>
     </row>
-    <row r="168" spans="3:57" ht="192" x14ac:dyDescent="0.2">
+    <row r="168" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C168" s="7" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="F168" s="13">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="J168" s="7" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="AN168" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO168" s="13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP168" s="14">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ168" s="13">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR168" s="14">
         <v>1</v>
@@ -18813,52 +18759,52 @@
       <c r="AS168" s="13">
         <v>1</v>
       </c>
-      <c r="AT168" s="15">
-        <v>0.3</v>
+      <c r="AT168" s="14">
+        <v>1</v>
       </c>
       <c r="AU168" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="AV168" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="AV168" s="14"/>
       <c r="AW168" s="17"/>
       <c r="BB168" s="13">
         <f t="shared" si="12"/>
-        <v>0.63333333333333341</v>
+        <v>1</v>
       </c>
       <c r="BC168" s="13">
         <f t="shared" si="13"/>
-        <v>0.63333333333333341</v>
+        <v>1</v>
       </c>
       <c r="BD168" s="13">
         <f t="shared" si="14"/>
-        <v>0.63333333333333341</v>
+        <v>1</v>
       </c>
       <c r="BE168" s="13">
         <f t="shared" si="15"/>
-        <v>0.56666666666666665</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="169" spans="3:57" ht="112" x14ac:dyDescent="0.2">
+    <row r="169" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C169" s="7" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>1196</v>
+        <v>887</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="F169" s="13">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="J169" s="7" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="AN169" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO169" s="13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP169" s="14">
         <v>1</v>
@@ -18867,51 +18813,51 @@
         <v>1</v>
       </c>
       <c r="AR169" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS169" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT169" s="16">
-        <v>0</v>
-      </c>
-      <c r="AU169" s="17">
-        <v>0</v>
-      </c>
-      <c r="AV169" s="16"/>
-      <c r="AW169" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="AT169" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU169" s="16">
+        <v>1</v>
+      </c>
+      <c r="AV169" s="15"/>
+      <c r="AW169" s="16"/>
       <c r="BB169" s="13">
         <f t="shared" si="12"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="BC169" s="13">
         <f t="shared" si="13"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="BD169" s="13">
         <f t="shared" si="14"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="BE169" s="13">
         <f t="shared" si="15"/>
-        <v>0.56666666666666665</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="170" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="170" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C170" s="7" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="F170" s="13">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="J170" s="7" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="AN170" s="13" t="s">
         <v>78</v>
@@ -18920,10 +18866,10 @@
         <v>1</v>
       </c>
       <c r="AP170" s="14">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AQ170" s="13">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AR170" s="14">
         <v>1</v>
@@ -18931,131 +18877,133 @@
       <c r="AS170" s="13">
         <v>1</v>
       </c>
-      <c r="AT170" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="AU170" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="AV170" s="14"/>
-      <c r="AW170" s="15"/>
+      <c r="AT170" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU170" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV170" s="15"/>
+      <c r="AW170" s="17"/>
       <c r="BB170" s="13">
         <f t="shared" si="12"/>
-        <v>0.53333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BC170" s="13">
         <f t="shared" si="13"/>
-        <v>0.53333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BD170" s="13">
         <f t="shared" si="14"/>
-        <v>0.53333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BE170" s="13">
         <f t="shared" si="15"/>
-        <v>0.76666666666666661</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="171" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="171" spans="3:57" ht="144" x14ac:dyDescent="0.2">
       <c r="C171" s="7" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>1167</v>
+        <v>1206</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="F171" s="13">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="J171" s="7" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="AN171" s="13" t="s">
         <v>67</v>
       </c>
       <c r="AO171" s="13">
-        <v>1</v>
-      </c>
-      <c r="AP171" s="14"/>
-      <c r="AQ171" s="16">
-        <v>0</v>
-      </c>
-      <c r="AR171" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS171" s="16">
-        <v>1</v>
-      </c>
-      <c r="AT171" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU171" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV171" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="AP171" s="16">
+        <v>1</v>
+      </c>
+      <c r="AQ171" s="17">
+        <v>1</v>
+      </c>
+      <c r="AR171" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="AS171" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="AT171" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="AU171" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="AV171" s="16">
+        <v>1</v>
+      </c>
+      <c r="AW171" s="17">
+        <v>1</v>
+      </c>
+      <c r="AX171" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="AY171" s="17">
         <v>0.3</v>
       </c>
-      <c r="AW171" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="AX171" s="14">
-        <v>1</v>
-      </c>
-      <c r="AY171" s="16">
-        <v>1</v>
-      </c>
-      <c r="AZ171" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="BA171" s="16">
-        <v>0.3</v>
+      <c r="AZ171" s="16">
+        <v>1</v>
+      </c>
+      <c r="BA171" s="17">
+        <v>0.6</v>
       </c>
       <c r="BB171" s="13">
         <f t="shared" si="12"/>
-        <v>0.72</v>
+        <v>0.80000000000000016</v>
       </c>
       <c r="BC171" s="13">
         <f t="shared" si="13"/>
-        <v>0.6</v>
+        <v>0.68333333333333324</v>
       </c>
       <c r="BD171" s="13">
         <f t="shared" si="14"/>
-        <v>0.65999999999999992</v>
+        <v>0.7416666666666667</v>
       </c>
       <c r="BE171" s="13">
         <f t="shared" si="15"/>
-        <v>0.83</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
-    <row r="172" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="172" spans="3:57" ht="144" x14ac:dyDescent="0.2">
       <c r="C172" s="7" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="F172" s="13">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="J172" s="7" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="AN172" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO172" s="13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP172" s="14">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AQ172" s="13">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AR172" s="14">
         <v>1</v>
@@ -19064,57 +19012,57 @@
         <v>1</v>
       </c>
       <c r="AT172" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU172" s="17">
-        <v>1</v>
+        <v>0.3</v>
+      </c>
+      <c r="AU172" s="15">
+        <v>0.3</v>
       </c>
       <c r="AV172" s="14"/>
-      <c r="AW172" s="17"/>
+      <c r="AW172" s="15"/>
       <c r="BB172" s="13">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BC172" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BD172" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BE172" s="13">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0.66666666666666674</v>
       </c>
     </row>
     <row r="173" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C173" s="7" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>887</v>
+        <v>1214</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="F173" s="13">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="J173" s="7" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="AN173" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO173" s="13">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AP173" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ173" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR173" s="14">
         <v>1</v>
@@ -19122,58 +19070,58 @@
       <c r="AS173" s="13">
         <v>1</v>
       </c>
-      <c r="AT173" s="15">
-        <v>1</v>
+      <c r="AT173" s="14">
+        <v>0.3</v>
       </c>
       <c r="AU173" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV173" s="15"/>
+        <v>0.3</v>
+      </c>
+      <c r="AV173" s="14"/>
       <c r="AW173" s="16"/>
       <c r="BB173" s="13">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BC173" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BD173" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BE173" s="13">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="174" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="174" spans="3:57" ht="112" x14ac:dyDescent="0.2">
       <c r="C174" s="7" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="F174" s="13">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="J174" s="7" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="AN174" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO174" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP174" s="14">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AQ174" s="13">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AR174" s="14">
         <v>1</v>
@@ -19181,369 +19129,395 @@
       <c r="AS174" s="13">
         <v>1</v>
       </c>
-      <c r="AT174" s="15">
-        <v>1</v>
+      <c r="AT174" s="14">
+        <v>0</v>
       </c>
       <c r="AU174" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV174" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="AV174" s="14"/>
       <c r="AW174" s="17"/>
       <c r="BB174" s="13">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BC174" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BD174" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BE174" s="13">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0.51666666666666661</v>
       </c>
     </row>
-    <row r="175" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="175" spans="3:57" ht="96" x14ac:dyDescent="0.2">
       <c r="C175" s="7" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="F175" s="13">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="J175" s="7" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="AN175" s="13" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="AO175" s="13">
         <v>0.8</v>
       </c>
-      <c r="AP175" s="16">
-        <v>1</v>
-      </c>
-      <c r="AQ175" s="17">
-        <v>1</v>
-      </c>
-      <c r="AR175" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AS175" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="AT175" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AU175" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="AV175" s="16">
-        <v>1</v>
-      </c>
-      <c r="AW175" s="17">
-        <v>1</v>
-      </c>
-      <c r="AX175" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AY175" s="17">
+      <c r="AP175" s="14">
         <v>0.3</v>
       </c>
-      <c r="AZ175" s="16">
-        <v>1</v>
-      </c>
-      <c r="BA175" s="17">
-        <v>0.6</v>
-      </c>
+      <c r="AQ175" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="AR175" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS175" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT175" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU175" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="AV175" s="15"/>
+      <c r="AW175" s="16"/>
       <c r="BB175" s="13">
         <f t="shared" si="12"/>
-        <v>0.80000000000000016</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BC175" s="13">
         <f t="shared" si="13"/>
-        <v>0.68333333333333324</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BD175" s="13">
         <f t="shared" si="14"/>
-        <v>0.7416666666666667</v>
+        <v>0.64999999999999991</v>
       </c>
       <c r="BE175" s="13">
         <f t="shared" si="15"/>
-        <v>0.77083333333333337</v>
+        <v>0.72499999999999998</v>
       </c>
     </row>
-    <row r="176" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="176" spans="3:57" ht="128" x14ac:dyDescent="0.2">
       <c r="C176" s="7" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="F176" s="13">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="J176" s="7" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="AN176" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO176" s="13">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AP176" s="14">
+        <v>1</v>
+      </c>
+      <c r="AQ176" s="13">
+        <v>1</v>
+      </c>
+      <c r="AR176" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS176" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT176" s="15">
         <v>0.3</v>
       </c>
-      <c r="AQ176" s="13">
+      <c r="AU176" s="17">
         <v>0.3</v>
       </c>
-      <c r="AR176" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS176" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT176" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="AU176" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="AV176" s="14"/>
-      <c r="AW176" s="15"/>
+      <c r="AV176" s="15"/>
+      <c r="AW176" s="17"/>
       <c r="BB176" s="13">
         <f t="shared" si="12"/>
-        <v>0.53333333333333333</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BC176" s="13">
         <f t="shared" si="13"/>
-        <v>0.53333333333333333</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BD176" s="13">
         <f t="shared" si="14"/>
-        <v>0.53333333333333333</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BE176" s="13">
         <f t="shared" si="15"/>
-        <v>0.66666666666666674</v>
+        <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="177" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="177" spans="3:57" ht="192" x14ac:dyDescent="0.2">
       <c r="C177" s="7" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="F177" s="13">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="J177" s="7" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="AN177" s="13" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AO177" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="AP177" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ177" s="13">
-        <v>0</v>
-      </c>
-      <c r="AR177" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS177" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT177" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="AP177" s="16">
+        <v>1</v>
+      </c>
+      <c r="AQ177" s="17">
+        <v>1</v>
+      </c>
+      <c r="AR177" s="16">
+        <v>1</v>
+      </c>
+      <c r="AS177" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="AT177" s="16">
         <v>0.3</v>
       </c>
-      <c r="AU177" s="16">
+      <c r="AU177" s="17">
         <v>0.3</v>
       </c>
-      <c r="AV177" s="14"/>
-      <c r="AW177" s="16"/>
+      <c r="AV177" s="16">
+        <v>1</v>
+      </c>
+      <c r="AW177" s="17">
+        <v>1</v>
+      </c>
+      <c r="AX177" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="AY177" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="AZ177" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="BA177" s="17">
+        <v>0.3</v>
+      </c>
       <c r="BB177" s="13">
         <f t="shared" si="12"/>
-        <v>0.43333333333333335</v>
+        <v>0.69999999999999984</v>
       </c>
       <c r="BC177" s="13">
         <f t="shared" si="13"/>
-        <v>0.43333333333333335</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="BD177" s="13">
         <f t="shared" si="14"/>
-        <v>0.43333333333333335</v>
+        <v>0.64166666666666661</v>
       </c>
       <c r="BE177" s="13">
         <f t="shared" si="15"/>
-        <v>0.41666666666666669</v>
+        <v>0.72083333333333333</v>
       </c>
     </row>
-    <row r="178" spans="3:57" ht="112" x14ac:dyDescent="0.2">
+    <row r="178" spans="3:57" ht="128" x14ac:dyDescent="0.2">
       <c r="C178" s="7" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="F178" s="13">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="J178" s="7" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="AN178" s="13" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="AO178" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="AP178" s="14">
+        <v>1</v>
+      </c>
+      <c r="AP178" s="14"/>
+      <c r="AQ178" s="15"/>
+      <c r="AR178" s="14">
         <v>0.6</v>
       </c>
-      <c r="AQ178" s="13">
+      <c r="AS178" s="15">
         <v>0.6</v>
       </c>
-      <c r="AR178" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS178" s="13">
-        <v>1</v>
-      </c>
       <c r="AT178" s="14">
-        <v>0</v>
-      </c>
-      <c r="AU178" s="17">
-        <v>0</v>
-      </c>
-      <c r="AV178" s="14"/>
-      <c r="AW178" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="AU178" s="15">
+        <v>1</v>
+      </c>
+      <c r="AV178" s="14">
+        <v>1</v>
+      </c>
+      <c r="AW178" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="AX178" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="AY178" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="AZ178" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="BA178" s="15">
+        <v>0.6</v>
+      </c>
       <c r="BB178" s="13">
         <f t="shared" si="12"/>
-        <v>0.53333333333333333</v>
+        <v>0.76</v>
       </c>
       <c r="BC178" s="13">
         <f t="shared" si="13"/>
-        <v>0.53333333333333333</v>
+        <v>0.68</v>
       </c>
       <c r="BD178" s="13">
         <f t="shared" si="14"/>
-        <v>0.53333333333333333</v>
+        <v>0.72</v>
       </c>
       <c r="BE178" s="13">
         <f t="shared" si="15"/>
-        <v>0.51666666666666661</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="179" spans="3:57" ht="96" x14ac:dyDescent="0.2">
       <c r="C179" s="7" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="F179" s="13">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="J179" s="7" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="AN179" s="13" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="AO179" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="AP179" s="14">
+        <v>0.4</v>
+      </c>
+      <c r="AP179" s="14"/>
+      <c r="AQ179" s="16">
+        <v>0</v>
+      </c>
+      <c r="AR179" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="AS179" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="AT179" s="14">
         <v>0.3</v>
-      </c>
-      <c r="AQ179" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="AR179" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS179" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT179" s="15">
-        <v>1</v>
       </c>
       <c r="AU179" s="16">
         <v>0.3</v>
       </c>
-      <c r="AV179" s="15"/>
-      <c r="AW179" s="16"/>
+      <c r="AV179" s="14">
+        <v>1</v>
+      </c>
+      <c r="AW179" s="16">
+        <v>1</v>
+      </c>
+      <c r="AX179" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="AY179" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="AZ179" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="BA179" s="16" t="s">
+        <v>1241</v>
+      </c>
       <c r="BB179" s="13">
         <f t="shared" si="12"/>
-        <v>0.76666666666666661</v>
+        <v>0.49999999999999989</v>
       </c>
       <c r="BC179" s="13">
         <f t="shared" si="13"/>
-        <v>0.53333333333333333</v>
+        <v>0.43999999999999995</v>
       </c>
       <c r="BD179" s="13">
         <f t="shared" si="14"/>
-        <v>0.64999999999999991</v>
+        <v>0.46999999999999992</v>
       </c>
       <c r="BE179" s="13">
         <f t="shared" si="15"/>
-        <v>0.72499999999999998</v>
+        <v>0.43499999999999994</v>
       </c>
     </row>
-    <row r="180" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="180" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C180" s="7" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="F180" s="13">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="J180" s="7" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="AN180" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO180" s="13">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AP180" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ180" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR180" s="14">
         <v>1</v>
@@ -19551,265 +19525,223 @@
       <c r="AS180" s="13">
         <v>1</v>
       </c>
-      <c r="AT180" s="15">
-        <v>0.3</v>
+      <c r="AT180" s="14">
+        <v>0.6</v>
       </c>
       <c r="AU180" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="AV180" s="15"/>
+        <v>0.6</v>
+      </c>
+      <c r="AV180" s="14"/>
       <c r="AW180" s="17"/>
       <c r="BB180" s="13">
         <f t="shared" si="12"/>
-        <v>0.76666666666666661</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BC180" s="13">
         <f t="shared" si="13"/>
-        <v>0.76666666666666661</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BD180" s="13">
         <f t="shared" si="14"/>
-        <v>0.76666666666666661</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BE180" s="13">
         <f t="shared" si="15"/>
-        <v>0.58333333333333326</v>
+        <v>0.76666666666666661</v>
       </c>
     </row>
-    <row r="181" spans="3:57" ht="192" x14ac:dyDescent="0.2">
+    <row r="181" spans="3:57" ht="208" x14ac:dyDescent="0.2">
       <c r="C181" s="7" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="F181" s="13">
         <v>2021</v>
       </c>
       <c r="J181" s="7" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="AN181" s="13" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="AO181" s="13">
         <v>0.8</v>
       </c>
-      <c r="AP181" s="16">
-        <v>1</v>
-      </c>
-      <c r="AQ181" s="17">
-        <v>1</v>
-      </c>
-      <c r="AR181" s="16">
-        <v>1</v>
-      </c>
-      <c r="AS181" s="17">
+      <c r="AP181" s="14">
         <v>0.6</v>
       </c>
-      <c r="AT181" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="AU181" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="AV181" s="16">
-        <v>1</v>
-      </c>
-      <c r="AW181" s="17">
-        <v>1</v>
-      </c>
-      <c r="AX181" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="AY181" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="AZ181" s="16">
+      <c r="AQ181" s="13">
         <v>0.6</v>
       </c>
-      <c r="BA181" s="17">
-        <v>0.3</v>
-      </c>
+      <c r="AR181" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS181" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT181" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU181" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="AV181" s="15"/>
+      <c r="AW181" s="16"/>
       <c r="BB181" s="13">
         <f t="shared" si="12"/>
-        <v>0.69999999999999984</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BC181" s="13">
         <f t="shared" si="13"/>
-        <v>0.58333333333333337</v>
+        <v>0.73333333333333339</v>
       </c>
       <c r="BD181" s="13">
         <f t="shared" si="14"/>
-        <v>0.64166666666666661</v>
+        <v>0.8</v>
       </c>
       <c r="BE181" s="13">
         <f t="shared" si="15"/>
-        <v>0.72083333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
-    <row r="182" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="182" spans="3:57" ht="192" x14ac:dyDescent="0.2">
       <c r="C182" s="7" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="F182" s="13">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="J182" s="7" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="AN182" s="13" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="AO182" s="13">
-        <v>1</v>
-      </c>
-      <c r="AP182" s="14"/>
-      <c r="AQ182" s="15"/>
+        <v>0.8</v>
+      </c>
+      <c r="AP182" s="14">
+        <v>1</v>
+      </c>
+      <c r="AQ182" s="13">
+        <v>1</v>
+      </c>
       <c r="AR182" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="AS182" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="AT182" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU182" s="15">
-        <v>1</v>
-      </c>
-      <c r="AV182" s="14">
-        <v>1</v>
-      </c>
-      <c r="AW182" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="AX182" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="AY182" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="AZ182" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="BA182" s="15">
-        <v>0.6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AS182" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT182" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU182" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV182" s="15"/>
+      <c r="AW182" s="17"/>
       <c r="BB182" s="13">
         <f t="shared" si="12"/>
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="BC182" s="13">
         <f t="shared" si="13"/>
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="BD182" s="13">
         <f t="shared" si="14"/>
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="BE182" s="13">
         <f t="shared" si="15"/>
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="183" spans="3:57" ht="96" x14ac:dyDescent="0.2">
       <c r="C183" s="7" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="F183" s="13">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="J183" s="7" t="s">
-        <v>1252</v>
-      </c>
-      <c r="AN183" s="13" t="s">
-        <v>67</v>
+        <v>1257</v>
+      </c>
+      <c r="AN183" s="18" t="s">
+        <v>78</v>
       </c>
       <c r="AO183" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="AP183" s="14"/>
-      <c r="AQ183" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="AP183" s="14">
+        <v>0</v>
+      </c>
+      <c r="AQ183" s="13">
         <v>0</v>
       </c>
       <c r="AR183" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="AS183" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AT183" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="AU183" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="AV183" s="14">
-        <v>1</v>
-      </c>
-      <c r="AW183" s="16">
-        <v>1</v>
-      </c>
-      <c r="AX183" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="AY183" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="AZ183" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="BA183" s="16" t="s">
-        <v>1253</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS183" s="13">
+        <v>0</v>
+      </c>
+      <c r="AT183" s="16">
+        <v>0</v>
+      </c>
+      <c r="AU183" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV183" s="16"/>
+      <c r="AW183" s="17"/>
       <c r="BB183" s="13">
         <f t="shared" si="12"/>
-        <v>0.49999999999999989</v>
+        <v>0</v>
       </c>
       <c r="BC183" s="13">
         <f t="shared" si="13"/>
-        <v>0.43999999999999995</v>
+        <v>0</v>
       </c>
       <c r="BD183" s="13">
         <f t="shared" si="14"/>
-        <v>0.46999999999999992</v>
+        <v>0</v>
       </c>
       <c r="BE183" s="13">
         <f t="shared" si="15"/>
-        <v>0.43499999999999994</v>
+        <v>0.25</v>
       </c>
     </row>
-    <row r="184" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="184" spans="3:57" ht="80" x14ac:dyDescent="0.2">
       <c r="C184" s="7" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="F184" s="13">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="J184" s="7" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="AN184" s="13" t="s">
         <v>78</v>
@@ -19818,10 +19750,10 @@
         <v>1</v>
       </c>
       <c r="AP184" s="14">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AQ184" s="13">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AR184" s="14">
         <v>1</v>
@@ -19832,43 +19764,43 @@
       <c r="AT184" s="14">
         <v>0.6</v>
       </c>
-      <c r="AU184" s="17">
+      <c r="AU184" s="15">
         <v>0.6</v>
       </c>
       <c r="AV184" s="14"/>
-      <c r="AW184" s="17"/>
+      <c r="AW184" s="15"/>
       <c r="BB184" s="13">
         <f t="shared" si="12"/>
-        <v>0.53333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="BC184" s="13">
         <f t="shared" si="13"/>
-        <v>0.53333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="BD184" s="13">
         <f t="shared" si="14"/>
-        <v>0.53333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="BE184" s="13">
         <f t="shared" si="15"/>
-        <v>0.76666666666666661</v>
+        <v>0.81666666666666665</v>
       </c>
     </row>
-    <row r="185" spans="3:57" ht="208" x14ac:dyDescent="0.2">
+    <row r="185" spans="3:57" ht="176" x14ac:dyDescent="0.2">
       <c r="C185" s="7" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="F185" s="13">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J185" s="7" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="AN185" s="13" t="s">
         <v>78</v>
@@ -19877,63 +19809,63 @@
         <v>0.8</v>
       </c>
       <c r="AP185" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="AQ185" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="AR185" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS185" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT185" s="14">
         <v>0.6</v>
-      </c>
-      <c r="AQ185" s="13">
-        <v>0.6</v>
-      </c>
-      <c r="AR185" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS185" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT185" s="15">
-        <v>1</v>
       </c>
       <c r="AU185" s="16">
         <v>0.6</v>
       </c>
-      <c r="AV185" s="15"/>
+      <c r="AV185" s="14"/>
       <c r="AW185" s="16"/>
       <c r="BB185" s="13">
         <f t="shared" si="12"/>
-        <v>0.8666666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="BC185" s="13">
         <f t="shared" si="13"/>
-        <v>0.73333333333333339</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="BD185" s="13">
         <f t="shared" si="14"/>
-        <v>0.8</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="BE185" s="13">
         <f t="shared" si="15"/>
-        <v>0.8</v>
+        <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="186" spans="3:57" ht="192" x14ac:dyDescent="0.2">
+    <row r="186" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C186" s="7" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="F186" s="13">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="J186" s="7" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="AN186" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO186" s="13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP186" s="14">
         <v>1</v>
@@ -19947,117 +19879,117 @@
       <c r="AS186" s="13">
         <v>1</v>
       </c>
-      <c r="AT186" s="15">
-        <v>1</v>
+      <c r="AT186" s="14">
+        <v>0.6</v>
       </c>
       <c r="AU186" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV186" s="15"/>
+        <v>0.6</v>
+      </c>
+      <c r="AV186" s="14"/>
       <c r="AW186" s="17"/>
       <c r="BB186" s="13">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BC186" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BD186" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BE186" s="13">
         <f t="shared" si="15"/>
-        <v>0.9</v>
+        <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="187" spans="3:57" ht="96" x14ac:dyDescent="0.2">
+    <row r="187" spans="3:57" ht="144" x14ac:dyDescent="0.2">
       <c r="C187" s="7" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="F187" s="13">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="J187" s="7" t="s">
-        <v>1269</v>
-      </c>
-      <c r="AN187" s="18" t="s">
+        <v>1273</v>
+      </c>
+      <c r="AN187" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO187" s="13">
         <v>0.5</v>
       </c>
       <c r="AP187" s="14">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AQ187" s="13">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AR187" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS187" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT187" s="16">
-        <v>0</v>
-      </c>
-      <c r="AU187" s="17">
-        <v>0</v>
-      </c>
-      <c r="AV187" s="16"/>
-      <c r="AW187" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="AT187" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU187" s="16">
+        <v>1</v>
+      </c>
+      <c r="AV187" s="15"/>
+      <c r="AW187" s="16"/>
       <c r="BB187" s="13">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BC187" s="13">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BD187" s="13">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BE187" s="13">
         <f t="shared" si="15"/>
-        <v>0.25</v>
+        <v>0.68333333333333335</v>
       </c>
     </row>
-    <row r="188" spans="3:57" ht="80" x14ac:dyDescent="0.2">
+    <row r="188" spans="3:57" ht="128" x14ac:dyDescent="0.2">
       <c r="C188" s="7" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="F188" s="13">
         <v>2022</v>
       </c>
       <c r="J188" s="7" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="AN188" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO188" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP188" s="14">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AQ188" s="13">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="AR188" s="14">
         <v>1</v>
@@ -20065,105 +19997,105 @@
       <c r="AS188" s="13">
         <v>1</v>
       </c>
-      <c r="AT188" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="AU188" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="AV188" s="14"/>
-      <c r="AW188" s="15"/>
+      <c r="AT188" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU188" s="17">
+        <v>1</v>
+      </c>
+      <c r="AV188" s="15"/>
+      <c r="AW188" s="17"/>
       <c r="BB188" s="13">
         <f t="shared" si="12"/>
-        <v>0.6333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BC188" s="13">
         <f t="shared" si="13"/>
-        <v>0.6333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BD188" s="13">
         <f t="shared" si="14"/>
-        <v>0.6333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BE188" s="13">
         <f t="shared" si="15"/>
-        <v>0.81666666666666665</v>
+        <v>0.75</v>
       </c>
     </row>
-    <row r="189" spans="3:57" ht="176" x14ac:dyDescent="0.2">
+    <row r="189" spans="3:57" ht="192" x14ac:dyDescent="0.2">
       <c r="C189" s="7" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="F189" s="13">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J189" s="7" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="AN189" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO189" s="13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP189" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="AQ189" s="13">
+        <v>0.6</v>
+      </c>
+      <c r="AR189" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS189" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT189" s="16">
         <v>0.3</v>
       </c>
-      <c r="AQ189" s="13">
+      <c r="AU189" s="17">
         <v>0.3</v>
       </c>
-      <c r="AR189" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS189" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT189" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="AU189" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AV189" s="14"/>
-      <c r="AW189" s="16"/>
+      <c r="AV189" s="16"/>
+      <c r="AW189" s="17"/>
       <c r="BB189" s="13">
         <f t="shared" si="12"/>
-        <v>0.6333333333333333</v>
+        <v>0.63333333333333341</v>
       </c>
       <c r="BC189" s="13">
         <f t="shared" si="13"/>
-        <v>0.6333333333333333</v>
+        <v>0.63333333333333341</v>
       </c>
       <c r="BD189" s="13">
         <f t="shared" si="14"/>
-        <v>0.6333333333333333</v>
+        <v>0.63333333333333341</v>
       </c>
       <c r="BE189" s="13">
         <f t="shared" si="15"/>
-        <v>0.71666666666666667</v>
+        <v>0.81666666666666665</v>
       </c>
     </row>
-    <row r="190" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="190" spans="3:57" ht="144" x14ac:dyDescent="0.2">
       <c r="C190" s="7" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="D190" s="7" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="F190" s="13">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J190" s="7" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="AN190" s="13" t="s">
         <v>78</v>
@@ -20172,128 +20104,144 @@
         <v>1</v>
       </c>
       <c r="AP190" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ190" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR190" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS190" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT190" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="AU190" s="17">
-        <v>0.6</v>
+        <v>1</v>
+      </c>
+      <c r="AU190" s="15">
+        <v>1</v>
       </c>
       <c r="AV190" s="14"/>
-      <c r="AW190" s="17"/>
+      <c r="AW190" s="15"/>
       <c r="BB190" s="13">
         <f t="shared" si="12"/>
-        <v>0.8666666666666667</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BC190" s="13">
         <f t="shared" si="13"/>
-        <v>0.8666666666666667</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BD190" s="13">
         <f t="shared" si="14"/>
-        <v>0.8666666666666667</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="BE190" s="13">
         <f t="shared" si="15"/>
-        <v>0.93333333333333335</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="191" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="191" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C191" s="7" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="E191" s="7" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="F191" s="13">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="J191" s="7" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="AN191" s="13" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AO191" s="13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP191" s="14">
+        <v>1</v>
+      </c>
+      <c r="AQ191" s="16">
+        <v>1</v>
+      </c>
+      <c r="AR191" s="14">
         <v>0.6</v>
       </c>
-      <c r="AQ191" s="13">
+      <c r="AS191" s="16">
         <v>0.6</v>
       </c>
-      <c r="AR191" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS191" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT191" s="15">
-        <v>1</v>
+      <c r="AT191" s="14">
+        <v>0.6</v>
       </c>
       <c r="AU191" s="16">
         <v>1</v>
       </c>
-      <c r="AV191" s="15"/>
-      <c r="AW191" s="16"/>
+      <c r="AV191" s="14">
+        <v>1</v>
+      </c>
+      <c r="AW191" s="16">
+        <v>1</v>
+      </c>
+      <c r="AX191" s="14">
+        <v>0</v>
+      </c>
+      <c r="AY191" s="16">
+        <v>0</v>
+      </c>
+      <c r="AZ191" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="BA191" s="16">
+        <v>0.6</v>
+      </c>
       <c r="BB191" s="13">
         <f t="shared" si="12"/>
-        <v>0.8666666666666667</v>
+        <v>0.63333333333333341</v>
       </c>
       <c r="BC191" s="13">
         <f t="shared" si="13"/>
-        <v>0.8666666666666667</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="BD191" s="13">
         <f t="shared" si="14"/>
-        <v>0.8666666666666667</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="BE191" s="13">
         <f t="shared" si="15"/>
-        <v>0.68333333333333335</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="192" spans="3:57" ht="128" x14ac:dyDescent="0.2">
+    <row r="192" spans="3:57" ht="176" x14ac:dyDescent="0.2">
       <c r="C192" s="7" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="E192" s="7" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="F192" s="13">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J192" s="7" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="AN192" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO192" s="13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP192" s="14">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AQ192" s="13">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AR192" s="14">
         <v>1</v>
@@ -20301,58 +20249,58 @@
       <c r="AS192" s="13">
         <v>1</v>
       </c>
-      <c r="AT192" s="15">
+      <c r="AT192" s="14">
         <v>1</v>
       </c>
       <c r="AU192" s="17">
         <v>1</v>
       </c>
-      <c r="AV192" s="15"/>
+      <c r="AV192" s="14"/>
       <c r="AW192" s="17"/>
       <c r="BB192" s="13">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BC192" s="13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BD192" s="13">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BE192" s="13">
         <f t="shared" si="15"/>
-        <v>0.75</v>
+        <v>0.8833333333333333</v>
       </c>
     </row>
-    <row r="193" spans="3:57" ht="192" x14ac:dyDescent="0.2">
+    <row r="193" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C193" s="7" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F193" s="13">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="J193" s="7" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="AN193" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO193" s="13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP193" s="14">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ193" s="13">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR193" s="14">
         <v>1</v>
@@ -20360,180 +20308,175 @@
       <c r="AS193" s="13">
         <v>1</v>
       </c>
-      <c r="AT193" s="16">
+      <c r="AT193" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU193" s="16">
         <v>0.3</v>
       </c>
-      <c r="AU193" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="AV193" s="16"/>
-      <c r="AW193" s="17"/>
+      <c r="AV193" s="15"/>
+      <c r="AW193" s="16"/>
       <c r="BB193" s="13">
         <f t="shared" si="12"/>
-        <v>0.63333333333333341</v>
+        <v>1</v>
       </c>
       <c r="BC193" s="13">
         <f t="shared" si="13"/>
-        <v>0.63333333333333341</v>
+        <v>0.76666666666666661</v>
       </c>
       <c r="BD193" s="13">
         <f t="shared" si="14"/>
-        <v>0.63333333333333341</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="BE193" s="13">
         <f t="shared" si="15"/>
-        <v>0.81666666666666665</v>
+        <v>0.84166666666666667</v>
       </c>
     </row>
-    <row r="194" spans="3:57" ht="144" x14ac:dyDescent="0.2">
+    <row r="194" spans="3:57" ht="160" x14ac:dyDescent="0.2">
       <c r="C194" s="7" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="F194" s="13">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="J194" s="7" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="AN194" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO194" s="13">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AP194" s="14">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AQ194" s="13">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AR194" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS194" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT194" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU194" s="15">
-        <v>1</v>
-      </c>
-      <c r="AV194" s="14"/>
-      <c r="AW194" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="AT194" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="AU194" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="AV194" s="15"/>
+      <c r="AW194" s="17"/>
       <c r="BB194" s="13">
         <f t="shared" si="12"/>
-        <v>0.33333333333333331</v>
+        <v>0.73333333333333339</v>
       </c>
       <c r="BC194" s="13">
         <f t="shared" si="13"/>
-        <v>0.33333333333333331</v>
+        <v>0.73333333333333339</v>
       </c>
       <c r="BD194" s="13">
         <f t="shared" si="14"/>
-        <v>0.33333333333333331</v>
+        <v>0.73333333333333339</v>
       </c>
       <c r="BE194" s="13">
         <f t="shared" si="15"/>
-        <v>0.66666666666666663</v>
+        <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="195" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="195" spans="3:57" ht="112" x14ac:dyDescent="0.2">
       <c r="C195" s="7" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D195" s="7" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="F195" s="13">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="J195" s="7" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="AN195" s="13" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="AO195" s="13">
-        <v>1</v>
-      </c>
-      <c r="AP195" s="14">
-        <v>1</v>
-      </c>
-      <c r="AQ195" s="16">
-        <v>1</v>
-      </c>
-      <c r="AR195" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="AP195" s="16">
+        <v>0</v>
+      </c>
+      <c r="AQ195" s="17"/>
+      <c r="AR195" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="AS195" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="AT195" s="16">
+        <v>0</v>
+      </c>
+      <c r="AU195" s="17">
+        <v>0</v>
+      </c>
+      <c r="AV195" s="16">
         <v>0.6</v>
       </c>
-      <c r="AS195" s="16">
+      <c r="AW195" s="17">
         <v>0.6</v>
       </c>
-      <c r="AT195" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="AU195" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV195" s="14">
-        <v>1</v>
-      </c>
-      <c r="AW195" s="16">
-        <v>1</v>
-      </c>
-      <c r="AX195" s="14">
-        <v>0</v>
-      </c>
-      <c r="AY195" s="16">
-        <v>0</v>
-      </c>
-      <c r="AZ195" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="BA195" s="16">
-        <v>0.6</v>
+      <c r="AX195" s="16">
+        <v>0</v>
+      </c>
+      <c r="AY195" s="17">
+        <v>0</v>
+      </c>
+      <c r="AZ195" s="16">
+        <v>1</v>
+      </c>
+      <c r="BA195" s="17">
+        <v>1</v>
       </c>
       <c r="BB195" s="13">
         <f t="shared" si="12"/>
-        <v>0.63333333333333341</v>
+        <v>0.31666666666666665</v>
       </c>
       <c r="BC195" s="13">
         <f t="shared" si="13"/>
-        <v>0.70000000000000007</v>
+        <v>0.38</v>
       </c>
       <c r="BD195" s="13">
         <f t="shared" si="14"/>
-        <v>0.66666666666666674</v>
+        <v>0.34833333333333333</v>
       </c>
       <c r="BE195" s="13">
         <f t="shared" si="15"/>
-        <v>0.83333333333333337</v>
+        <v>0.42416666666666669</v>
       </c>
     </row>
-    <row r="196" spans="3:57" ht="176" x14ac:dyDescent="0.2">
+    <row r="196" spans="3:57" ht="192" x14ac:dyDescent="0.2">
       <c r="C196" s="7" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>1291</v>
+        <v>1305</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="F196" s="13">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="J196" s="7" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="AN196" s="13" t="s">
         <v>78</v>
@@ -20542,462 +20485,215 @@
         <v>1</v>
       </c>
       <c r="AP196" s="14">
+        <v>0</v>
+      </c>
+      <c r="AQ196" s="13">
+        <v>0</v>
+      </c>
+      <c r="AR196" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS196" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT196" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="AU196" s="15">
         <v>0.3</v>
       </c>
-      <c r="AQ196" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="AR196" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS196" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT196" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU196" s="17">
-        <v>1</v>
-      </c>
       <c r="AV196" s="14"/>
-      <c r="AW196" s="17"/>
+      <c r="AW196" s="15"/>
       <c r="BB196" s="13">
         <f t="shared" si="12"/>
-        <v>0.76666666666666661</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="BC196" s="13">
         <f t="shared" si="13"/>
-        <v>0.76666666666666661</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BD196" s="13">
         <f t="shared" si="14"/>
-        <v>0.76666666666666661</v>
+        <v>0.48333333333333334</v>
       </c>
       <c r="BE196" s="13">
         <f t="shared" si="15"/>
-        <v>0.8833333333333333</v>
+        <v>0.7416666666666667</v>
       </c>
     </row>
-    <row r="197" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="197" spans="3:57" ht="176" x14ac:dyDescent="0.2">
       <c r="C197" s="7" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>1306</v>
+        <v>1051</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="F197" s="13">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="J197" s="7" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="AN197" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO197" s="13">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP197" s="14">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AQ197" s="13">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AR197" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS197" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT197" s="15">
+        <v>0</v>
+      </c>
+      <c r="AT197" s="14">
         <v>1</v>
       </c>
       <c r="AU197" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="AV197" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="AV197" s="14"/>
       <c r="AW197" s="16"/>
       <c r="BB197" s="13">
         <f t="shared" si="12"/>
-        <v>1</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BC197" s="13">
         <f t="shared" si="13"/>
-        <v>0.76666666666666661</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BD197" s="13">
         <f t="shared" si="14"/>
-        <v>0.8833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="BE197" s="13">
         <f t="shared" si="15"/>
-        <v>0.84166666666666667</v>
+        <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="198" spans="3:57" ht="160" x14ac:dyDescent="0.2">
+    <row r="198" spans="3:57" ht="288" x14ac:dyDescent="0.2">
       <c r="C198" s="7" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="E198" s="7" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="F198" s="13">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="J198" s="7" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="AN198" s="13" t="s">
         <v>78</v>
       </c>
       <c r="AO198" s="13">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AP198" s="14">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ198" s="13">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR198" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS198" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT198" s="15">
-        <v>0.6</v>
+        <v>0</v>
+      </c>
+      <c r="AT198" s="14">
+        <v>1</v>
       </c>
       <c r="AU198" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="AV198" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="AV198" s="14"/>
       <c r="AW198" s="17"/>
       <c r="BB198" s="13">
         <f t="shared" si="12"/>
-        <v>0.73333333333333339</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BC198" s="13">
         <f t="shared" si="13"/>
-        <v>0.73333333333333339</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BD198" s="13">
         <f t="shared" si="14"/>
-        <v>0.73333333333333339</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="BE198" s="13">
         <f t="shared" si="15"/>
-        <v>0.76666666666666672</v>
+        <v>0.58333333333333326</v>
       </c>
     </row>
-    <row r="199" spans="3:57" ht="112" x14ac:dyDescent="0.2">
+    <row r="199" spans="3:57" ht="128" x14ac:dyDescent="0.2">
       <c r="C199" s="7" t="s">
-        <v>1313</v>
+        <v>1315</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>887</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="F199" s="13">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="AN199" s="13" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="AO199" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="AP199" s="16">
-        <v>0</v>
-      </c>
-      <c r="AQ199" s="17"/>
-      <c r="AR199" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="AS199" s="17">
-        <v>0.3</v>
-      </c>
-      <c r="AT199" s="16">
-        <v>0</v>
-      </c>
-      <c r="AU199" s="17">
-        <v>0</v>
-      </c>
-      <c r="AV199" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AW199" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="AX199" s="16">
-        <v>0</v>
-      </c>
-      <c r="AY199" s="17">
-        <v>0</v>
-      </c>
-      <c r="AZ199" s="16">
-        <v>1</v>
-      </c>
-      <c r="BA199" s="17">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AP199" s="14">
+        <v>1</v>
+      </c>
+      <c r="AQ199" s="13">
+        <v>1</v>
+      </c>
+      <c r="AR199" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS199" s="13">
+        <v>1</v>
+      </c>
+      <c r="AT199" s="15">
+        <v>1</v>
+      </c>
+      <c r="AU199" s="16">
+        <v>1</v>
+      </c>
+      <c r="AV199" s="15"/>
+      <c r="AW199" s="16"/>
       <c r="BB199" s="13">
         <f t="shared" si="12"/>
-        <v>0.31666666666666665</v>
+        <v>1</v>
       </c>
       <c r="BC199" s="13">
         <f t="shared" si="13"/>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="BD199" s="13">
         <f t="shared" si="14"/>
-        <v>0.34833333333333333</v>
+        <v>1</v>
       </c>
       <c r="BE199" s="13">
-        <f t="shared" si="15"/>
-        <v>0.42416666666666669</v>
-      </c>
-    </row>
-    <row r="200" spans="3:57" ht="192" x14ac:dyDescent="0.2">
-      <c r="C200" s="7" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D200" s="7" t="s">
-        <v>1317</v>
-      </c>
-      <c r="E200" s="7" t="s">
-        <v>1318</v>
-      </c>
-      <c r="F200" s="13">
-        <v>2024</v>
-      </c>
-      <c r="J200" s="7" t="s">
-        <v>1319</v>
-      </c>
-      <c r="AN200" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO200" s="13">
-        <v>1</v>
-      </c>
-      <c r="AP200" s="14">
-        <v>0</v>
-      </c>
-      <c r="AQ200" s="13">
-        <v>0</v>
-      </c>
-      <c r="AR200" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS200" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT200" s="14">
-        <v>0.6</v>
-      </c>
-      <c r="AU200" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="AV200" s="14"/>
-      <c r="AW200" s="15"/>
-      <c r="BB200" s="13">
-        <f t="shared" si="12"/>
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="BC200" s="13">
-        <f t="shared" si="13"/>
-        <v>0.43333333333333335</v>
-      </c>
-      <c r="BD200" s="13">
-        <f t="shared" si="14"/>
-        <v>0.48333333333333334</v>
-      </c>
-      <c r="BE200" s="13">
-        <f t="shared" si="15"/>
-        <v>0.7416666666666667</v>
-      </c>
-    </row>
-    <row r="201" spans="3:57" ht="176" x14ac:dyDescent="0.2">
-      <c r="C201" s="7" t="s">
-        <v>1320</v>
-      </c>
-      <c r="D201" s="7" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E201" s="7" t="s">
-        <v>1321</v>
-      </c>
-      <c r="F201" s="13">
-        <v>2024</v>
-      </c>
-      <c r="J201" s="7" t="s">
-        <v>1322</v>
-      </c>
-      <c r="AN201" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO201" s="13">
-        <v>1</v>
-      </c>
-      <c r="AP201" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="AQ201" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="AR201" s="14">
-        <v>0</v>
-      </c>
-      <c r="AS201" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT201" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU201" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV201" s="14"/>
-      <c r="AW201" s="16"/>
-      <c r="BB201" s="13">
-        <f t="shared" si="12"/>
-        <v>0.43333333333333335</v>
-      </c>
-      <c r="BC201" s="13">
-        <f t="shared" si="13"/>
-        <v>0.43333333333333335</v>
-      </c>
-      <c r="BD201" s="13">
-        <f t="shared" si="14"/>
-        <v>0.43333333333333335</v>
-      </c>
-      <c r="BE201" s="13">
-        <f t="shared" si="15"/>
-        <v>0.71666666666666667</v>
-      </c>
-    </row>
-    <row r="202" spans="3:57" ht="288" x14ac:dyDescent="0.2">
-      <c r="C202" s="7" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D202" s="7" t="s">
-        <v>1324</v>
-      </c>
-      <c r="E202" s="7" t="s">
-        <v>1325</v>
-      </c>
-      <c r="F202" s="13">
-        <v>2020</v>
-      </c>
-      <c r="J202" s="7" t="s">
-        <v>1326</v>
-      </c>
-      <c r="AN202" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO202" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="AP202" s="14">
-        <v>1</v>
-      </c>
-      <c r="AQ202" s="13">
-        <v>1</v>
-      </c>
-      <c r="AR202" s="14">
-        <v>0</v>
-      </c>
-      <c r="AS202" s="13">
-        <v>0</v>
-      </c>
-      <c r="AT202" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU202" s="17">
-        <v>1</v>
-      </c>
-      <c r="AV202" s="14"/>
-      <c r="AW202" s="17"/>
-      <c r="BB202" s="13">
-        <f t="shared" si="12"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="BC202" s="13">
-        <f t="shared" si="13"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="BD202" s="13">
-        <f t="shared" si="14"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="BE202" s="13">
-        <f t="shared" si="15"/>
-        <v>0.58333333333333326</v>
-      </c>
-    </row>
-    <row r="203" spans="3:57" ht="128" x14ac:dyDescent="0.2">
-      <c r="C203" s="7" t="s">
-        <v>1327</v>
-      </c>
-      <c r="D203" s="7" t="s">
-        <v>887</v>
-      </c>
-      <c r="E203" s="7" t="s">
-        <v>1328</v>
-      </c>
-      <c r="F203" s="13">
-        <v>2015</v>
-      </c>
-      <c r="J203" s="7" t="s">
-        <v>1329</v>
-      </c>
-      <c r="AN203" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO203" s="13">
-        <v>1</v>
-      </c>
-      <c r="AP203" s="14">
-        <v>1</v>
-      </c>
-      <c r="AQ203" s="13">
-        <v>1</v>
-      </c>
-      <c r="AR203" s="14">
-        <v>1</v>
-      </c>
-      <c r="AS203" s="13">
-        <v>1</v>
-      </c>
-      <c r="AT203" s="15">
-        <v>1</v>
-      </c>
-      <c r="AU203" s="16">
-        <v>1</v>
-      </c>
-      <c r="AV203" s="15"/>
-      <c r="AW203" s="16"/>
-      <c r="BB203" s="13">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
-      <c r="BC203" s="13">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BD203" s="13">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="BE203" s="13">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
@@ -21034,26 +20730,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ab92c565-5003-4ac3-93a3-a3ce8796a3c0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B6889C2593FACB4192549183B8B19287" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="32060b2073082e2092342fdaa07ba96e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ab92c565-5003-4ac3-93a3-a3ce8796a3c0" xmlns:ns3="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="930e06c061e109ec993a06acfd2977e1" ns2:_="" ns3:_="">
     <xsd:import namespace="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
@@ -21248,26 +20924,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75C2E995-E4B5-43AB-976A-D7C66C193ADA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
-    <ds:schemaRef ds:uri="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{943FC6A1-4453-4C1A-9E7F-BF39CEFF06B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ab92c565-5003-4ac3-93a3-a3ce8796a3c0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E930122-8DA5-429F-A725-BB94052D8ABA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21284,4 +20961,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{943FC6A1-4453-4C1A-9E7F-BF39CEFF06B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75C2E995-E4B5-43AB-976A-D7C66C193ADA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ab92c565-5003-4ac3-93a3-a3ce8796a3c0"/>
+    <ds:schemaRef ds:uri="aa1b21cb-23df-461b-8b8e-4aaeac2f3f50"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>